--- a/Stock_list.xlsx
+++ b/Stock_list.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="72" windowWidth="22632" windowHeight="9192" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="72" windowWidth="20712" windowHeight="9192" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="TW50" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="183">
   <si>
     <t>股票代號</t>
   </si>
@@ -91,15 +91,6 @@
   </si>
   <si>
     <t>中信金</t>
-  </si>
-  <si>
-    <t>新光金</t>
-  </si>
-  <si>
-    <t>中壽</t>
-  </si>
-  <si>
-    <t>晶電</t>
   </si>
   <si>
     <t>南亞</t>
@@ -953,7 +944,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -969,7 +960,7 @@
         <v>1301</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -977,7 +968,7 @@
         <v>1303</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -985,7 +976,7 @@
         <v>2002</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -993,7 +984,7 @@
         <v>2059</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -1001,7 +992,7 @@
         <v>2207</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -1009,7 +1000,7 @@
         <v>2301</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -1025,7 +1016,7 @@
         <v>2308</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -1041,7 +1032,7 @@
         <v>2327</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -1049,7 +1040,7 @@
         <v>2330</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -1057,7 +1048,7 @@
         <v>2344</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -1065,7 +1056,7 @@
         <v>2345</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -1073,7 +1064,7 @@
         <v>2357</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -1081,7 +1072,7 @@
         <v>2360</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -1089,7 +1080,7 @@
         <v>2368</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -1097,7 +1088,7 @@
         <v>2382</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -1105,7 +1096,7 @@
         <v>2383</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -1113,7 +1104,7 @@
         <v>2395</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -1121,7 +1112,7 @@
         <v>2408</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -1137,7 +1128,7 @@
         <v>2449</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
@@ -1145,7 +1136,7 @@
         <v>2454</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -1153,7 +1144,7 @@
         <v>2603</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
@@ -1161,7 +1152,7 @@
         <v>2880</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -1185,7 +1176,7 @@
         <v>2883</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
@@ -1201,7 +1192,7 @@
         <v>2885</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
@@ -1217,7 +1208,7 @@
         <v>2887</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
@@ -1225,7 +1216,7 @@
         <v>2890</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
@@ -1241,7 +1232,7 @@
         <v>2892</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -1257,7 +1248,7 @@
         <v>3017</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
@@ -1265,7 +1256,7 @@
         <v>3037</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
@@ -1273,7 +1264,7 @@
         <v>3045</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
@@ -1281,7 +1272,7 @@
         <v>3231</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
@@ -1289,7 +1280,7 @@
         <v>3653</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
@@ -1297,7 +1288,7 @@
         <v>3661</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
@@ -1305,7 +1296,7 @@
         <v>3711</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
@@ -1321,7 +1312,7 @@
         <v>5880</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
@@ -1329,7 +1320,7 @@
         <v>6505</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -1337,7 +1328,7 @@
         <v>6669</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -1345,7 +1336,7 @@
         <v>6919</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -1353,7 +1344,7 @@
         <v>7769</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1372,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -1380,7 +1371,7 @@
         <v>1101</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1388,7 +1379,7 @@
         <v>1102</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -1404,7 +1395,7 @@
         <v>1229</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -1412,7 +1403,7 @@
         <v>1319</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -1420,7 +1411,7 @@
         <v>1326</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -1428,7 +1419,7 @@
         <v>1402</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -1436,7 +1427,7 @@
         <v>1451</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -1444,7 +1435,7 @@
         <v>1476</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -1452,7 +1443,7 @@
         <v>1477</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -1460,7 +1451,7 @@
         <v>1503</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -1468,7 +1459,7 @@
         <v>1504</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -1476,7 +1467,7 @@
         <v>1513</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -1484,7 +1475,7 @@
         <v>1519</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -1492,7 +1483,7 @@
         <v>1560</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="32.4" x14ac:dyDescent="0.3">
@@ -1500,7 +1491,7 @@
         <v>1590</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -1508,7 +1499,7 @@
         <v>1605</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -1516,7 +1507,7 @@
         <v>1718</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -1524,7 +1515,7 @@
         <v>1795</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -1532,7 +1523,7 @@
         <v>1802</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="32.4" x14ac:dyDescent="0.3">
@@ -1540,7 +1531,7 @@
         <v>2006</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -1548,7 +1539,7 @@
         <v>2027</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -1572,7 +1563,7 @@
         <v>2207</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="32.4" x14ac:dyDescent="0.3">
@@ -1580,7 +1571,7 @@
         <v>2258</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -1588,7 +1579,7 @@
         <v>2312</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
@@ -1596,7 +1587,7 @@
         <v>2313</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
@@ -1604,7 +1595,7 @@
         <v>2324</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
@@ -1612,7 +1603,7 @@
         <v>2337</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -1620,7 +1611,7 @@
         <v>2347</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
@@ -1628,7 +1619,7 @@
         <v>2353</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
@@ -1644,7 +1635,7 @@
         <v>2356</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
@@ -1660,7 +1651,7 @@
         <v>2376</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -1668,7 +1659,7 @@
         <v>2377</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -1676,7 +1667,7 @@
         <v>2379</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
@@ -1684,7 +1675,7 @@
         <v>2385</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
@@ -1692,7 +1683,7 @@
         <v>2404</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
@@ -1700,7 +1691,7 @@
         <v>2409</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
@@ -1708,7 +1699,7 @@
         <v>2451</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
@@ -1716,7 +1707,7 @@
         <v>2474</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
@@ -1724,7 +1715,7 @@
         <v>2478</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
@@ -1732,7 +1723,7 @@
         <v>2539</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
@@ -1748,7 +1739,7 @@
         <v>2609</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -1756,7 +1747,7 @@
         <v>2610</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -1764,7 +1755,7 @@
         <v>2615</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -1772,7 +1763,7 @@
         <v>2618</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="32.4" x14ac:dyDescent="0.3">
@@ -1780,7 +1771,7 @@
         <v>2633</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="32.4" x14ac:dyDescent="0.3">
@@ -1788,7 +1779,7 @@
         <v>2645</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="32.4" x14ac:dyDescent="0.3">
@@ -1796,7 +1787,7 @@
         <v>2646</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -1804,7 +1795,7 @@
         <v>2801</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -1812,7 +1803,7 @@
         <v>2812</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -1820,7 +1811,7 @@
         <v>2834</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -1828,7 +1819,7 @@
         <v>2838</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -1836,7 +1827,7 @@
         <v>2845</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -1860,7 +1851,7 @@
         <v>3005</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
@@ -1868,7 +1859,7 @@
         <v>3023</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
@@ -1876,7 +1867,7 @@
         <v>3034</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
@@ -1884,7 +1875,7 @@
         <v>3036</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -1892,7 +1883,7 @@
         <v>3044</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
@@ -1900,7 +1891,7 @@
         <v>3051</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
@@ -1908,7 +1899,7 @@
         <v>3189</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
@@ -1916,7 +1907,7 @@
         <v>3443</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
@@ -1924,7 +1915,7 @@
         <v>3481</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
@@ -1932,7 +1923,7 @@
         <v>3533</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="32.4" x14ac:dyDescent="0.3">
@@ -1940,7 +1931,7 @@
         <v>3665</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
@@ -1948,7 +1939,7 @@
         <v>3702</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
@@ -1956,7 +1947,7 @@
         <v>3706</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="32.4" x14ac:dyDescent="0.3">
@@ -1964,7 +1955,7 @@
         <v>4137</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="32.4" x14ac:dyDescent="0.3">
@@ -1972,7 +1963,7 @@
         <v>4583</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
@@ -1980,7 +1971,7 @@
         <v>4938</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="32.4" x14ac:dyDescent="0.3">
@@ -1988,7 +1979,7 @@
         <v>4958</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
@@ -1996,7 +1987,7 @@
         <v>5269</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="32.4" x14ac:dyDescent="0.3">
@@ -2004,7 +1995,7 @@
         <v>5871</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="81" spans="1:2" ht="32.4" x14ac:dyDescent="0.3">
@@ -2012,7 +2003,7 @@
         <v>5876</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
@@ -2020,7 +2011,7 @@
         <v>6005</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
@@ -2028,7 +2019,7 @@
         <v>6139</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
@@ -2036,7 +2027,7 @@
         <v>6176</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
@@ -2052,7 +2043,7 @@
         <v>6285</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
@@ -2060,7 +2051,7 @@
         <v>6409</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="88" spans="1:2" ht="32.4" x14ac:dyDescent="0.3">
@@ -2068,7 +2059,7 @@
         <v>6415</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
@@ -2076,7 +2067,7 @@
         <v>6442</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
@@ -2084,7 +2075,7 @@
         <v>6446</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
@@ -2092,7 +2083,7 @@
         <v>6472</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
@@ -2100,7 +2091,7 @@
         <v>6515</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
@@ -2108,7 +2099,7 @@
         <v>6526</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
@@ -2116,7 +2107,7 @@
         <v>6531</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
@@ -2124,7 +2115,7 @@
         <v>6770</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="96" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
@@ -2132,7 +2123,7 @@
         <v>6781</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
@@ -2140,7 +2131,7 @@
         <v>6789</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
@@ -2148,7 +2139,7 @@
         <v>6805</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="99" spans="1:2" ht="32.4" x14ac:dyDescent="0.3">
@@ -2156,7 +2147,7 @@
         <v>6890</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
@@ -2164,7 +2155,7 @@
         <v>7750</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
@@ -2172,7 +2163,7 @@
         <v>7799</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
@@ -2180,7 +2171,7 @@
         <v>8046</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
@@ -2188,7 +2179,7 @@
         <v>8210</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
@@ -2196,7 +2187,7 @@
         <v>8454</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
@@ -2204,7 +2195,7 @@
         <v>8464</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
@@ -2212,7 +2203,7 @@
         <v>8996</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
@@ -2228,7 +2219,7 @@
         <v>9910</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
@@ -2236,7 +2227,7 @@
         <v>9945</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2247,7 +2238,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B98"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
@@ -2259,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -2456,7 +2447,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>2888</v>
+        <v>1303</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>25</v>
@@ -2464,7 +2455,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>2823</v>
+        <v>2207</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>26</v>
@@ -2472,7 +2463,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>2448</v>
+        <v>1227</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>27</v>
@@ -2480,7 +2471,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>1303</v>
+        <v>2330</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>28</v>
@@ -2488,7 +2479,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>2207</v>
+        <v>2610</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>29</v>
@@ -2496,7 +2487,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>1227</v>
+        <v>2707</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>30</v>
@@ -2504,7 +2495,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>2330</v>
+        <v>2204</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>31</v>
@@ -2512,7 +2503,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>2610</v>
+        <v>3045</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>32</v>
@@ -2520,7 +2511,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>2707</v>
+        <v>2903</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>33</v>
@@ -2528,7 +2519,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>2204</v>
+        <v>2880</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>34</v>
@@ -2536,7 +2527,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>3045</v>
+        <v>2834</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>35</v>
@@ -2544,7 +2535,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>2903</v>
+        <v>9945</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>36</v>
@@ -2552,7 +2543,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>2880</v>
+        <v>4938</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>37</v>
@@ -2560,7 +2551,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>2834</v>
+        <v>2892</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>38</v>
@@ -2568,7 +2559,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <v>9945</v>
+        <v>2801</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>39</v>
@@ -2576,7 +2567,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>4938</v>
+        <v>2015</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>40</v>
@@ -2584,7 +2575,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>2892</v>
+        <v>2615</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>41</v>
@@ -2592,7 +2583,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>2801</v>
+        <v>2002</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>42</v>
@@ -2600,7 +2591,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
-        <v>2015</v>
+        <v>1301</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>43</v>
@@ -2608,7 +2599,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
-        <v>2615</v>
+        <v>6176</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>44</v>
@@ -2616,7 +2607,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
-        <v>2002</v>
+        <v>3702</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>45</v>
@@ -2624,7 +2615,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
-        <v>1301</v>
+        <v>1434</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>46</v>
@@ -2632,7 +2623,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
-        <v>6176</v>
+        <v>2890</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>47</v>
@@ -2640,7 +2631,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
-        <v>3702</v>
+        <v>2618</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>48</v>
@@ -2648,7 +2639,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
-        <v>1434</v>
+        <v>2353</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>49</v>
@@ -2656,7 +2647,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
-        <v>2890</v>
+        <v>2347</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>50</v>
@@ -2664,7 +2655,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
-        <v>2618</v>
+        <v>6005</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>51</v>
@@ -2672,7 +2663,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <v>2353</v>
+        <v>1326</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>52</v>
@@ -2680,7 +2671,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
-        <v>2347</v>
+        <v>1402</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>53</v>
@@ -2688,7 +2679,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
-        <v>6005</v>
+        <v>1717</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>54</v>
@@ -2696,7 +2687,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
-        <v>1326</v>
+        <v>2883</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>55</v>
@@ -2704,7 +2695,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
-        <v>1402</v>
+        <v>2609</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>56</v>
@@ -2712,7 +2703,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
-        <v>1717</v>
+        <v>2395</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>57</v>
@@ -2720,39 +2711,39 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
-        <v>2883</v>
+        <v>2301</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
-        <v>2609</v>
+        <v>6121</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
-        <v>2395</v>
+        <v>2885</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
-        <v>2301</v>
+        <v>2362</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
-        <v>6121</v>
+        <v>2201</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>66</v>
@@ -2760,306 +2751,282 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
-        <v>2885</v>
+        <v>2392</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
-        <v>2362</v>
+        <v>3231</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <v>2201</v>
+        <v>1101</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
-        <v>2392</v>
+        <v>2356</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
-        <v>3231</v>
+        <v>1605</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
-        <v>1101</v>
+        <v>6505</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
-        <v>2356</v>
+        <v>2385</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
-        <v>1605</v>
+        <v>1102</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
-        <v>6505</v>
+        <v>2451</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
-        <v>2385</v>
+        <v>6244</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <v>1102</v>
+        <v>2409</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
-        <v>2451</v>
+        <v>1722</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <v>6244</v>
+        <v>1314</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
-        <v>2409</v>
+        <v>2606</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
-        <v>1722</v>
+        <v>1802</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
-        <v>1314</v>
+        <v>2474</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
-        <v>2606</v>
+        <v>2308</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
-        <v>1802</v>
+        <v>2337</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
-        <v>2474</v>
+        <v>1504</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
-        <v>2308</v>
+        <v>2454</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
-        <v>2337</v>
+        <v>2101</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
-        <v>1504</v>
+        <v>2393</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
-        <v>2454</v>
+        <v>2324</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
-        <v>2101</v>
+        <v>3034</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
-        <v>2393</v>
+        <v>2357</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
-        <v>2324</v>
+        <v>2103</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
-        <v>3034</v>
+        <v>2379</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
-        <v>2357</v>
+        <v>3044</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
-        <v>2103</v>
+        <v>3037</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
-        <v>2379</v>
+        <v>3189</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
-        <v>3044</v>
+        <v>8069</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
-        <v>3037</v>
+        <v>8046</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
-        <v>3189</v>
+        <v>5483</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
-        <v>8069</v>
+        <v>8299</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
-        <v>8046</v>
+        <v>2382</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A99" s="2">
-        <v>5483</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A100" s="2">
-        <v>8299</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A101" s="2">
-        <v>2382</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/Stock_list.xlsx
+++ b/Stock_list.xlsx
@@ -2500,10 +2500,363 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:B44"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>股票代號</v>
+      </c>
+      <c r="B1" t="str">
+        <v>股票名稱</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>3576</v>
+      </c>
+      <c r="B2" t="str">
+        <v>聯合再生</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>8112</v>
+      </c>
+      <c r="B3" t="str">
+        <v>至上</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2406</v>
+      </c>
+      <c r="B4" t="str">
+        <v>國碩</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>6443</v>
+      </c>
+      <c r="B5" t="str">
+        <v>元晶</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>0056</v>
+      </c>
+      <c r="B6" t="str">
+        <v>元大高股息</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2867</v>
+      </c>
+      <c r="B7" t="str">
+        <v>三商壽</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>8039</v>
+      </c>
+      <c r="B8" t="str">
+        <v>台虹</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>8105</v>
+      </c>
+      <c r="B9" t="str">
+        <v>凌巨</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2355</v>
+      </c>
+      <c r="B10" t="str">
+        <v>敬鵬</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>6153</v>
+      </c>
+      <c r="B11" t="str">
+        <v>嘉聯益</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1714</v>
+      </c>
+      <c r="B12" t="str">
+        <v>和桐</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>0050</v>
+      </c>
+      <c r="B13" t="str">
+        <v>元大台灣50</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2014</v>
+      </c>
+      <c r="B14" t="str">
+        <v>中鴻</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2515</v>
+      </c>
+      <c r="B15" t="str">
+        <v>中工</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2323</v>
+      </c>
+      <c r="B16" t="str">
+        <v>中環</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2637</v>
+      </c>
+      <c r="B17" t="str">
+        <v>慧洋-KY</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2402</v>
+      </c>
+      <c r="B18" t="str">
+        <v>毅嘉</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>6706</v>
+      </c>
+      <c r="B19" t="str">
+        <v>惠特</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>6278</v>
+      </c>
+      <c r="B20" t="str">
+        <v>台表科</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2441</v>
+      </c>
+      <c r="B21" t="str">
+        <v>超豐</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>8021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>尖點</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>3532</v>
+      </c>
+      <c r="B23" t="str">
+        <v>台勝科</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2458</v>
+      </c>
+      <c r="B24" t="str">
+        <v>義隆</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>3167</v>
+      </c>
+      <c r="B25" t="str">
+        <v>大量</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>5434</v>
+      </c>
+      <c r="B26" t="str">
+        <v>崇越</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2455</v>
+      </c>
+      <c r="B27" t="str">
+        <v>全新</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>3090</v>
+      </c>
+      <c r="B28" t="str">
+        <v>日電貿</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>8150</v>
+      </c>
+      <c r="B29" t="str">
+        <v>南茂</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>1210</v>
+      </c>
+      <c r="B30" t="str">
+        <v>大成</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>4915</v>
+      </c>
+      <c r="B31" t="str">
+        <v>致伸</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2206</v>
+      </c>
+      <c r="B32" t="str">
+        <v>三陽工業</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>6271</v>
+      </c>
+      <c r="B33" t="str">
+        <v>同欣電</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>9917</v>
+      </c>
+      <c r="B34" t="str">
+        <v>中保科</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>3042</v>
+      </c>
+      <c r="B35" t="str">
+        <v>晶技</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2481</v>
+      </c>
+      <c r="B36" t="str">
+        <v>強茂</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>6196</v>
+      </c>
+      <c r="B37" t="str">
+        <v>帆宣</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>5243</v>
+      </c>
+      <c r="B38" t="str">
+        <v>乙盛-KY</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>8028</v>
+      </c>
+      <c r="B39" t="str">
+        <v>昇陽半導體</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>1215</v>
+      </c>
+      <c r="B40" t="str">
+        <v>卜蜂</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2548</v>
+      </c>
+      <c r="B41" t="str">
+        <v>華固</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>6831</v>
+      </c>
+      <c r="B42" t="str">
+        <v>邁科</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>2211</v>
+      </c>
+      <c r="B43" t="str">
+        <v>長榮鋼</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>2492</v>
+      </c>
+      <c r="B44" t="str">
+        <v>華新科</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B44"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Stock_list.xlsx
+++ b/Stock_list.xlsx
@@ -2500,7 +2500,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:G151"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2510,7 +2510,7 @@
         <v>股票名稱</v>
       </c>
       <c r="C1" t="str">
-        <v>買超張數</v>
+        <v>購買張數</v>
       </c>
       <c r="D1" t="str">
         <v>來源法人</v>
@@ -2519,872 +2519,3465 @@
         <v>法人內排名</v>
       </c>
       <c r="F1" t="str">
-        <v>抓取日期</v>
+        <v>比對備註</v>
+      </c>
+      <c r="G1" t="str">
+        <v>交易日期</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>3576</v>
+        <v>2356</v>
       </c>
       <c r="B2" t="str">
-        <v>聯合再生</v>
+        <v>英業達</v>
       </c>
       <c r="C2">
-        <v>30962798</v>
+        <v>10164000</v>
       </c>
       <c r="D2" t="str">
         <v>外資</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F2" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G2" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>8112</v>
+        <v>2888</v>
       </c>
       <c r="B3" t="str">
-        <v>至上</v>
+        <v>新光金</v>
       </c>
       <c r="C3">
-        <v>459843</v>
+        <v>8438000</v>
       </c>
       <c r="D3" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F3" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G3" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2406</v>
+        <v>2883</v>
       </c>
       <c r="B4" t="str">
-        <v>國碩</v>
+        <v>凱基金</v>
       </c>
       <c r="C4">
-        <v>16057013</v>
+        <v>5660887</v>
       </c>
       <c r="D4" t="str">
         <v>外資</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F4" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G4" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>6443</v>
+        <v>2498</v>
       </c>
       <c r="B5" t="str">
-        <v>元晶</v>
+        <v>宏達電</v>
       </c>
       <c r="C5">
-        <v>13937107</v>
+        <v>5359000</v>
       </c>
       <c r="D5" t="str">
         <v>外資</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F5" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G5" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>0056</v>
+        <v>1605</v>
       </c>
       <c r="B6" t="str">
-        <v>元大高股息</v>
+        <v>華新</v>
       </c>
       <c r="C6">
-        <v>12930903</v>
+        <v>5231257</v>
       </c>
       <c r="D6" t="str">
         <v>外資</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F6" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G6" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2867</v>
+        <v>2891</v>
       </c>
       <c r="B7" t="str">
-        <v>三商壽</v>
+        <v>中信金</v>
       </c>
       <c r="C7">
-        <v>10280930</v>
+        <v>4849000</v>
       </c>
       <c r="D7" t="str">
         <v>外資</v>
       </c>
       <c r="E7">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F7" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G7" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>8039</v>
+        <v>5469</v>
       </c>
       <c r="B8" t="str">
-        <v>台虹</v>
+        <v>瀚宇博</v>
       </c>
       <c r="C8">
-        <v>7535049</v>
+        <v>4722000</v>
       </c>
       <c r="D8" t="str">
         <v>外資</v>
       </c>
       <c r="E8">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="F8" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G8" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>8105</v>
+        <v>2301</v>
       </c>
       <c r="B9" t="str">
-        <v>凌巨</v>
+        <v>光寶科</v>
       </c>
       <c r="C9">
-        <v>7187206</v>
+        <v>2968000</v>
       </c>
       <c r="D9" t="str">
         <v>外資</v>
       </c>
       <c r="E9">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="F9" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G9" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2355</v>
+        <v>1710</v>
       </c>
       <c r="B10" t="str">
-        <v>敬鵬</v>
+        <v>東聯</v>
       </c>
       <c r="C10">
-        <v>6868332</v>
+        <v>2714000</v>
       </c>
       <c r="D10" t="str">
         <v>外資</v>
       </c>
       <c r="E10">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F10" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G10" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>6153</v>
+        <v>2412</v>
       </c>
       <c r="B11" t="str">
-        <v>嘉聯益</v>
+        <v>中華電</v>
       </c>
       <c r="C11">
-        <v>6823395</v>
+        <v>2342931</v>
       </c>
       <c r="D11" t="str">
         <v>外資</v>
       </c>
       <c r="E11">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F11" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G11" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1714</v>
+        <v>2610</v>
       </c>
       <c r="B12" t="str">
-        <v>和桐</v>
+        <v>華航</v>
       </c>
       <c r="C12">
-        <v>5811300</v>
+        <v>2075000</v>
       </c>
       <c r="D12" t="str">
         <v>外資</v>
       </c>
       <c r="E12">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F12" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G12" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>0050</v>
+        <v>2618</v>
       </c>
       <c r="B13" t="str">
-        <v>元大台灣50</v>
+        <v>長榮航</v>
       </c>
       <c r="C13">
-        <v>4830000</v>
+        <v>2065000</v>
       </c>
       <c r="D13" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
       <c r="E13">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F13" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G13" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2014</v>
+        <v>1229</v>
       </c>
       <c r="B14" t="str">
-        <v>中鴻</v>
+        <v>聯華</v>
       </c>
       <c r="C14">
-        <v>5576124</v>
+        <v>1982000</v>
       </c>
       <c r="D14" t="str">
         <v>外資</v>
       </c>
       <c r="E14">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F14" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G14" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2515</v>
+        <v>2881</v>
       </c>
       <c r="B15" t="str">
-        <v>中工</v>
+        <v>富邦金</v>
       </c>
       <c r="C15">
-        <v>4361156</v>
+        <v>1879000</v>
       </c>
       <c r="D15" t="str">
         <v>外資</v>
       </c>
       <c r="E15">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="F15" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G15" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2323</v>
+        <v>2337</v>
       </c>
       <c r="B16" t="str">
-        <v>中環</v>
+        <v>旺宏</v>
       </c>
       <c r="C16">
-        <v>4305452</v>
+        <v>1723000</v>
       </c>
       <c r="D16" t="str">
         <v>外資</v>
       </c>
       <c r="E16">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="F16" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G16" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2637</v>
+        <v>2325</v>
       </c>
       <c r="B17" t="str">
-        <v>慧洋-KY</v>
+        <v>矽品</v>
       </c>
       <c r="C17">
-        <v>2505215</v>
+        <v>1506949</v>
       </c>
       <c r="D17" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
       <c r="E17">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F17" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G17" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2402</v>
+        <v>2313</v>
       </c>
       <c r="B18" t="str">
-        <v>毅嘉</v>
+        <v>華通</v>
       </c>
       <c r="C18">
-        <v>3171566</v>
+        <v>1367000</v>
       </c>
       <c r="D18" t="str">
         <v>外資</v>
       </c>
       <c r="E18">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F18" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G18" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>6706</v>
+        <v>3596</v>
       </c>
       <c r="B19" t="str">
-        <v>惠特</v>
+        <v>智易</v>
       </c>
       <c r="C19">
-        <v>1293000</v>
+        <v>1295000</v>
       </c>
       <c r="D19" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
       <c r="E19">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F19" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G19" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>6278</v>
+        <v>2455</v>
       </c>
       <c r="B20" t="str">
-        <v>台表科</v>
+        <v>全新</v>
       </c>
       <c r="C20">
-        <v>479606</v>
+        <v>1270000</v>
       </c>
       <c r="D20" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
       <c r="E20">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F20" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G20" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2441</v>
+        <v>6278</v>
       </c>
       <c r="B21" t="str">
-        <v>超豐</v>
+        <v>台表科</v>
       </c>
       <c r="C21">
-        <v>875000</v>
+        <v>1076000</v>
       </c>
       <c r="D21" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
       <c r="E21">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F21" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G21" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>8021</v>
+        <v>4938</v>
       </c>
       <c r="B22" t="str">
-        <v>尖點</v>
+        <v>和碩</v>
       </c>
       <c r="C22">
-        <v>707000</v>
+        <v>961710</v>
       </c>
       <c r="D22" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
       <c r="E22">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F22" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G22" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>3532</v>
+        <v>1718</v>
       </c>
       <c r="B23" t="str">
-        <v>台勝科</v>
+        <v>中纖</v>
       </c>
       <c r="C23">
-        <v>444000</v>
+        <v>938000</v>
       </c>
       <c r="D23" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
       <c r="E23">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F23" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G23" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2458</v>
+        <v>3005</v>
       </c>
       <c r="B24" t="str">
-        <v>義隆</v>
+        <v>神基</v>
       </c>
       <c r="C24">
-        <v>214853</v>
+        <v>936200</v>
       </c>
       <c r="D24" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
       <c r="E24">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F24" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G24" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>3167</v>
+        <v>1704</v>
       </c>
       <c r="B25" t="str">
-        <v>大量</v>
+        <v>榮化</v>
       </c>
       <c r="C25">
-        <v>253000</v>
+        <v>908000</v>
       </c>
       <c r="D25" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
       <c r="E25">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F25" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G25" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>5434</v>
+        <v>2449</v>
       </c>
       <c r="B26" t="str">
-        <v>崇越</v>
+        <v>京元電子</v>
       </c>
       <c r="C26">
-        <v>183000</v>
+        <v>894000</v>
       </c>
       <c r="D26" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
       <c r="E26">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F26" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G26" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2455</v>
+        <v>2417</v>
       </c>
       <c r="B27" t="str">
-        <v>全新</v>
+        <v>圓剛</v>
       </c>
       <c r="C27">
-        <v>147000</v>
+        <v>893000</v>
       </c>
       <c r="D27" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
       <c r="E27">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="F27" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G27" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>3090</v>
+        <v>2344</v>
       </c>
       <c r="B28" t="str">
-        <v>日電貿</v>
+        <v>華邦電</v>
       </c>
       <c r="C28">
-        <v>3797511</v>
+        <v>883001</v>
       </c>
       <c r="D28" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
       <c r="E28">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="F28" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G28" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>8150</v>
+        <v>1609</v>
       </c>
       <c r="B29" t="str">
-        <v>南茂</v>
+        <v>大亞</v>
       </c>
       <c r="C29">
-        <v>2704000</v>
+        <v>863000</v>
       </c>
       <c r="D29" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
       <c r="E29">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F29" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G29" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>1210</v>
+        <v>1326</v>
       </c>
       <c r="B30" t="str">
-        <v>大成</v>
+        <v>台化</v>
       </c>
       <c r="C30">
-        <v>1692000</v>
+        <v>810551</v>
       </c>
       <c r="D30" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
       <c r="E30">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F30" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G30" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>4915</v>
+        <v>2359</v>
       </c>
       <c r="B31" t="str">
-        <v>致伸</v>
+        <v>所羅門</v>
       </c>
       <c r="C31">
-        <v>1644878</v>
+        <v>790000</v>
       </c>
       <c r="D31" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
       <c r="E31">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F31" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G31" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2206</v>
+        <v>3026</v>
       </c>
       <c r="B32" t="str">
-        <v>三陽工業</v>
+        <v>禾伸堂</v>
       </c>
       <c r="C32">
-        <v>1242696</v>
+        <v>755000</v>
       </c>
       <c r="D32" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
       <c r="E32">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F32" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G32" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>6271</v>
+        <v>2448</v>
       </c>
       <c r="B33" t="str">
-        <v>同欣電</v>
+        <v>晶電</v>
       </c>
       <c r="C33">
-        <v>1057000</v>
+        <v>746000</v>
       </c>
       <c r="D33" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
       <c r="E33">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F33" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G33" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>9917</v>
+        <v>6505</v>
       </c>
       <c r="B34" t="str">
-        <v>中保科</v>
+        <v>台塑化</v>
       </c>
       <c r="C34">
-        <v>918000</v>
+        <v>746000</v>
       </c>
       <c r="D34" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
       <c r="E34">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F34" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G34" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>3042</v>
+        <v>2104</v>
       </c>
       <c r="B35" t="str">
-        <v>晶技</v>
+        <v>國際中橡</v>
       </c>
       <c r="C35">
-        <v>778000</v>
+        <v>746000</v>
       </c>
       <c r="D35" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
       <c r="E35">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F35" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G35" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2481</v>
+        <v>2347</v>
       </c>
       <c r="B36" t="str">
-        <v>強茂</v>
+        <v>聯強</v>
       </c>
       <c r="C36">
-        <v>657000</v>
+        <v>726000</v>
       </c>
       <c r="D36" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
       <c r="E36">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F36" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G36" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>6196</v>
+        <v>6191</v>
       </c>
       <c r="B37" t="str">
-        <v>帆宣</v>
+        <v>精成科</v>
       </c>
       <c r="C37">
-        <v>623000</v>
+        <v>715000</v>
       </c>
       <c r="D37" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
       <c r="E37">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F37" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G37" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>5243</v>
+        <v>3090</v>
       </c>
       <c r="B38" t="str">
-        <v>乙盛-KY</v>
+        <v>日電貿</v>
       </c>
       <c r="C38">
-        <v>500000</v>
+        <v>703000</v>
       </c>
       <c r="D38" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
       <c r="E38">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F38" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G38" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>8028</v>
+        <v>2371</v>
       </c>
       <c r="B39" t="str">
-        <v>昇陽半導體</v>
+        <v>大同</v>
       </c>
       <c r="C39">
-        <v>238000</v>
+        <v>691000</v>
       </c>
       <c r="D39" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
       <c r="E39">
         <v>38</v>
       </c>
       <c r="F39" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G39" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>1215</v>
+        <v>3682</v>
       </c>
       <c r="B40" t="str">
-        <v>卜蜂</v>
+        <v>亞太電</v>
       </c>
       <c r="C40">
-        <v>224000</v>
+        <v>689000</v>
       </c>
       <c r="D40" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
       <c r="E40">
         <v>39</v>
       </c>
       <c r="F40" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G40" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2548</v>
+        <v>2474</v>
       </c>
       <c r="B41" t="str">
-        <v>華固</v>
+        <v>可成</v>
       </c>
       <c r="C41">
-        <v>174000</v>
+        <v>684000</v>
       </c>
       <c r="D41" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
       <c r="E41">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F41" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G41" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>6831</v>
+        <v>9939</v>
       </c>
       <c r="B42" t="str">
-        <v>邁科</v>
+        <v>宏全</v>
       </c>
       <c r="C42">
-        <v>133000</v>
+        <v>677000</v>
       </c>
       <c r="D42" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
       <c r="E42">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F42" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G42" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2211</v>
+        <v>4904</v>
       </c>
       <c r="B43" t="str">
-        <v>長榮鋼</v>
+        <v>遠傳</v>
       </c>
       <c r="C43">
-        <v>125434</v>
+        <v>661964</v>
       </c>
       <c r="D43" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
       <c r="E43">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F43" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G43" t="str">
         <v>20260612</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
+        <v>2603</v>
+      </c>
+      <c r="B44" t="str">
+        <v>長榮</v>
+      </c>
+      <c r="C44">
+        <v>641987</v>
+      </c>
+      <c r="D44" t="str">
+        <v>外資</v>
+      </c>
+      <c r="E44">
+        <v>43</v>
+      </c>
+      <c r="F44" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G44" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>2614</v>
+      </c>
+      <c r="B45" t="str">
+        <v>東森</v>
+      </c>
+      <c r="C45">
+        <v>603000</v>
+      </c>
+      <c r="D45" t="str">
+        <v>外資</v>
+      </c>
+      <c r="E45">
+        <v>44</v>
+      </c>
+      <c r="F45" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G45" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
         <v>2492</v>
       </c>
-      <c r="B44" t="str">
+      <c r="B46" t="str">
         <v>華新科</v>
       </c>
-      <c r="C44">
+      <c r="C46">
+        <v>586000</v>
+      </c>
+      <c r="D46" t="str">
+        <v>外資</v>
+      </c>
+      <c r="E46">
+        <v>45</v>
+      </c>
+      <c r="F46" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G46" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>2023</v>
+      </c>
+      <c r="B47" t="str">
+        <v>燁輝</v>
+      </c>
+      <c r="C47">
+        <v>575280</v>
+      </c>
+      <c r="D47" t="str">
+        <v>外資</v>
+      </c>
+      <c r="E47">
+        <v>46</v>
+      </c>
+      <c r="F47" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G47" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>2515</v>
+      </c>
+      <c r="B48" t="str">
+        <v>中工</v>
+      </c>
+      <c r="C48">
+        <v>536000</v>
+      </c>
+      <c r="D48" t="str">
+        <v>外資</v>
+      </c>
+      <c r="E48">
+        <v>47</v>
+      </c>
+      <c r="F48" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G48" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>1310</v>
+      </c>
+      <c r="B49" t="str">
+        <v>台苯</v>
+      </c>
+      <c r="C49">
+        <v>530000</v>
+      </c>
+      <c r="D49" t="str">
+        <v>外資</v>
+      </c>
+      <c r="E49">
+        <v>48</v>
+      </c>
+      <c r="F49" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G49" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>9904</v>
+      </c>
+      <c r="B50" t="str">
+        <v>寶成</v>
+      </c>
+      <c r="C50">
+        <v>521931</v>
+      </c>
+      <c r="D50" t="str">
+        <v>外資</v>
+      </c>
+      <c r="E50">
+        <v>49</v>
+      </c>
+      <c r="F50" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G50" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2633</v>
+      </c>
+      <c r="B51" t="str">
+        <v>台灣高鐵</v>
+      </c>
+      <c r="C51">
+        <v>520000</v>
+      </c>
+      <c r="D51" t="str">
+        <v>外資</v>
+      </c>
+      <c r="E51">
+        <v>50</v>
+      </c>
+      <c r="F51" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G51" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>1909</v>
+      </c>
+      <c r="B52" t="str">
+        <v>榮成</v>
+      </c>
+      <c r="C52">
+        <v>1702000</v>
+      </c>
+      <c r="D52" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+      <c r="F52" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G52" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>2845</v>
+      </c>
+      <c r="B53" t="str">
+        <v>遠東銀</v>
+      </c>
+      <c r="C53">
+        <v>1202000</v>
+      </c>
+      <c r="D53" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E53">
+        <v>2</v>
+      </c>
+      <c r="F53" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G53" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>3702</v>
+      </c>
+      <c r="B54" t="str">
+        <v>大聯大</v>
+      </c>
+      <c r="C54">
+        <v>1147000</v>
+      </c>
+      <c r="D54" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E54">
+        <v>3</v>
+      </c>
+      <c r="F54" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G54" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>4919</v>
+      </c>
+      <c r="B55" t="str">
+        <v>新唐</v>
+      </c>
+      <c r="C55">
+        <v>1051000</v>
+      </c>
+      <c r="D55" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E55">
+        <v>4</v>
+      </c>
+      <c r="F55" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G55" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>2456</v>
+      </c>
+      <c r="B56" t="str">
+        <v>奇力新</v>
+      </c>
+      <c r="C56">
+        <v>850000</v>
+      </c>
+      <c r="D56" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E56">
+        <v>5</v>
+      </c>
+      <c r="F56" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G56" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>2603</v>
+      </c>
+      <c r="B57" t="str">
+        <v>長榮</v>
+      </c>
+      <c r="C57">
+        <v>715000</v>
+      </c>
+      <c r="D57" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E57">
+        <v>6</v>
+      </c>
+      <c r="F57" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G57" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>2449</v>
+      </c>
+      <c r="B58" t="str">
+        <v>京元電子</v>
+      </c>
+      <c r="C58">
+        <v>665000</v>
+      </c>
+      <c r="D58" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E58">
+        <v>7</v>
+      </c>
+      <c r="F58" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G58" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>1710</v>
+      </c>
+      <c r="B59" t="str">
+        <v>東聯</v>
+      </c>
+      <c r="C59">
+        <v>591000</v>
+      </c>
+      <c r="D59" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E59">
+        <v>8</v>
+      </c>
+      <c r="F59" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G59" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>2330</v>
+      </c>
+      <c r="B60" t="str">
+        <v>台積電</v>
+      </c>
+      <c r="C60">
+        <v>559000</v>
+      </c>
+      <c r="D60" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E60">
+        <v>9</v>
+      </c>
+      <c r="F60" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G60" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>2311</v>
+      </c>
+      <c r="B61" t="str">
+        <v>日月光</v>
+      </c>
+      <c r="C61">
+        <v>481000</v>
+      </c>
+      <c r="D61" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E61">
+        <v>10</v>
+      </c>
+      <c r="F61" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G61" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>2204</v>
+      </c>
+      <c r="B62" t="str">
+        <v>中華</v>
+      </c>
+      <c r="C62">
+        <v>451000</v>
+      </c>
+      <c r="D62" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E62">
+        <v>11</v>
+      </c>
+      <c r="F62" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G62" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>4532</v>
+      </c>
+      <c r="B63" t="str">
+        <v>瑞智</v>
+      </c>
+      <c r="C63">
+        <v>442000</v>
+      </c>
+      <c r="D63" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E63">
+        <v>12</v>
+      </c>
+      <c r="F63" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G63" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>2104</v>
+      </c>
+      <c r="B64" t="str">
+        <v>國際中橡</v>
+      </c>
+      <c r="C64">
+        <v>393000</v>
+      </c>
+      <c r="D64" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E64">
+        <v>13</v>
+      </c>
+      <c r="F64" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G64" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>2317</v>
+      </c>
+      <c r="B65" t="str">
+        <v>鴻海</v>
+      </c>
+      <c r="C65">
+        <v>376000</v>
+      </c>
+      <c r="D65" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E65">
+        <v>14</v>
+      </c>
+      <c r="F65" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G65" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>2377</v>
+      </c>
+      <c r="B66" t="str">
+        <v>微星</v>
+      </c>
+      <c r="C66">
+        <v>332000</v>
+      </c>
+      <c r="D66" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E66">
+        <v>15</v>
+      </c>
+      <c r="F66" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G66" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>4915</v>
+      </c>
+      <c r="B67" t="str">
+        <v>致伸</v>
+      </c>
+      <c r="C67">
+        <v>306000</v>
+      </c>
+      <c r="D67" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E67">
+        <v>16</v>
+      </c>
+      <c r="F67" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G67" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>2501</v>
+      </c>
+      <c r="B68" t="str">
+        <v>國建</v>
+      </c>
+      <c r="C68">
+        <v>294000</v>
+      </c>
+      <c r="D68" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E68">
+        <v>17</v>
+      </c>
+      <c r="F68" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G68" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>9941</v>
+      </c>
+      <c r="B69" t="str">
+        <v>裕融</v>
+      </c>
+      <c r="C69">
+        <v>267000</v>
+      </c>
+      <c r="D69" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E69">
+        <v>18</v>
+      </c>
+      <c r="F69" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G69" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>2618</v>
+      </c>
+      <c r="B70" t="str">
+        <v>長榮航</v>
+      </c>
+      <c r="C70">
+        <v>259000</v>
+      </c>
+      <c r="D70" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E70">
+        <v>19</v>
+      </c>
+      <c r="F70" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G70" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>3006</v>
+      </c>
+      <c r="B71" t="str">
+        <v>晶豪科</v>
+      </c>
+      <c r="C71">
+        <v>258000</v>
+      </c>
+      <c r="D71" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E71">
+        <v>20</v>
+      </c>
+      <c r="F71" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G71" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>1507</v>
+      </c>
+      <c r="B72" t="str">
+        <v>永大</v>
+      </c>
+      <c r="C72">
+        <v>251000</v>
+      </c>
+      <c r="D72" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E72">
+        <v>21</v>
+      </c>
+      <c r="F72" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G72" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>5871</v>
+      </c>
+      <c r="B73" t="str">
+        <v>中租-KY</v>
+      </c>
+      <c r="C73">
+        <v>251000</v>
+      </c>
+      <c r="D73" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E73">
+        <v>22</v>
+      </c>
+      <c r="F73" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G73" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>3022</v>
+      </c>
+      <c r="B74" t="str">
+        <v>威強電</v>
+      </c>
+      <c r="C74">
+        <v>234000</v>
+      </c>
+      <c r="D74" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E74">
+        <v>23</v>
+      </c>
+      <c r="F74" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G74" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>2015</v>
+      </c>
+      <c r="B75" t="str">
+        <v>豐興</v>
+      </c>
+      <c r="C75">
+        <v>224000</v>
+      </c>
+      <c r="D75" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E75">
+        <v>24</v>
+      </c>
+      <c r="F75" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G75" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>5243</v>
+      </c>
+      <c r="B76" t="str">
+        <v>乙盛-KY</v>
+      </c>
+      <c r="C76">
+        <v>217000</v>
+      </c>
+      <c r="D76" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E76">
+        <v>25</v>
+      </c>
+      <c r="F76" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G76" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>1305</v>
+      </c>
+      <c r="B77" t="str">
+        <v>華夏</v>
+      </c>
+      <c r="C77">
+        <v>212000</v>
+      </c>
+      <c r="D77" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E77">
+        <v>26</v>
+      </c>
+      <c r="F77" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G77" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>5007</v>
+      </c>
+      <c r="B78" t="str">
+        <v>三星</v>
+      </c>
+      <c r="C78">
+        <v>210000</v>
+      </c>
+      <c r="D78" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E78">
+        <v>27</v>
+      </c>
+      <c r="F78" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G78" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>2421</v>
+      </c>
+      <c r="B79" t="str">
+        <v>建準</v>
+      </c>
+      <c r="C79">
+        <v>203000</v>
+      </c>
+      <c r="D79" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E79">
+        <v>28</v>
+      </c>
+      <c r="F79" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G79" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>2344</v>
+      </c>
+      <c r="B80" t="str">
+        <v>華邦電</v>
+      </c>
+      <c r="C80">
+        <v>200000</v>
+      </c>
+      <c r="D80" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E80">
+        <v>29</v>
+      </c>
+      <c r="F80" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G80" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>1319</v>
+      </c>
+      <c r="B81" t="str">
+        <v>東陽</v>
+      </c>
+      <c r="C81">
+        <v>200000</v>
+      </c>
+      <c r="D81" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E81">
+        <v>30</v>
+      </c>
+      <c r="F81" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G81" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>6196</v>
+      </c>
+      <c r="B82" t="str">
+        <v>帆宣</v>
+      </c>
+      <c r="C82">
+        <v>191000</v>
+      </c>
+      <c r="D82" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E82">
+        <v>31</v>
+      </c>
+      <c r="F82" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G82" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>2454</v>
+      </c>
+      <c r="B83" t="str">
+        <v>聯發科</v>
+      </c>
+      <c r="C83">
+        <v>171000</v>
+      </c>
+      <c r="D83" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E83">
+        <v>32</v>
+      </c>
+      <c r="F83" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G83" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>5305</v>
+      </c>
+      <c r="B84" t="str">
+        <v>敦南</v>
+      </c>
+      <c r="C84">
+        <v>154000</v>
+      </c>
+      <c r="D84" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E84">
+        <v>33</v>
+      </c>
+      <c r="F84" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G84" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>2408</v>
+      </c>
+      <c r="B85" t="str">
+        <v>南亞科</v>
+      </c>
+      <c r="C85">
+        <v>150000</v>
+      </c>
+      <c r="D85" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E85">
+        <v>34</v>
+      </c>
+      <c r="F85" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G85" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>6271</v>
+      </c>
+      <c r="B86" t="str">
+        <v>同欣電</v>
+      </c>
+      <c r="C86">
+        <v>148000</v>
+      </c>
+      <c r="D86" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E86">
+        <v>35</v>
+      </c>
+      <c r="F86" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G86" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>3044</v>
+      </c>
+      <c r="B87" t="str">
+        <v>健鼎</v>
+      </c>
+      <c r="C87">
+        <v>148000</v>
+      </c>
+      <c r="D87" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E87">
+        <v>36</v>
+      </c>
+      <c r="F87" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G87" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>3042</v>
+      </c>
+      <c r="B88" t="str">
+        <v>晶技</v>
+      </c>
+      <c r="C88">
+        <v>145000</v>
+      </c>
+      <c r="D88" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E88">
+        <v>37</v>
+      </c>
+      <c r="F88" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G88" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>4551</v>
+      </c>
+      <c r="B89" t="str">
+        <v>智伸科</v>
+      </c>
+      <c r="C89">
+        <v>142000</v>
+      </c>
+      <c r="D89" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E89">
+        <v>38</v>
+      </c>
+      <c r="F89" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G89" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>2455</v>
+      </c>
+      <c r="B90" t="str">
+        <v>全新</v>
+      </c>
+      <c r="C90">
+        <v>132000</v>
+      </c>
+      <c r="D90" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E90">
+        <v>39</v>
+      </c>
+      <c r="F90" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G90" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>9904</v>
+      </c>
+      <c r="B91" t="str">
+        <v>寶成</v>
+      </c>
+      <c r="C91">
+        <v>130000</v>
+      </c>
+      <c r="D91" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E91">
+        <v>40</v>
+      </c>
+      <c r="F91" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G91" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>2345</v>
+      </c>
+      <c r="B92" t="str">
+        <v>智邦</v>
+      </c>
+      <c r="C92">
+        <v>128000</v>
+      </c>
+      <c r="D92" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E92">
+        <v>41</v>
+      </c>
+      <c r="F92" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G92" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>3443</v>
+      </c>
+      <c r="B93" t="str">
+        <v>創意</v>
+      </c>
+      <c r="C93">
+        <v>127000</v>
+      </c>
+      <c r="D93" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E93">
+        <v>42</v>
+      </c>
+      <c r="F93" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G93" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>2404</v>
+      </c>
+      <c r="B94" t="str">
+        <v>漢唐</v>
+      </c>
+      <c r="C94">
+        <v>126000</v>
+      </c>
+      <c r="D94" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E94">
+        <v>43</v>
+      </c>
+      <c r="F94" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G94" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>2228</v>
+      </c>
+      <c r="B95" t="str">
+        <v>劍麟</v>
+      </c>
+      <c r="C95">
         <v>106000</v>
       </c>
-      <c r="D44" t="str">
+      <c r="D95" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E95">
+        <v>44</v>
+      </c>
+      <c r="F95" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G95" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>3645</v>
+      </c>
+      <c r="B96" t="str">
+        <v>達邁</v>
+      </c>
+      <c r="C96">
+        <v>100000</v>
+      </c>
+      <c r="D96" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E96">
+        <v>45</v>
+      </c>
+      <c r="F96" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G96" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>6153</v>
+      </c>
+      <c r="B97" t="str">
+        <v>嘉聯益</v>
+      </c>
+      <c r="C97">
+        <v>100000</v>
+      </c>
+      <c r="D97" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E97">
+        <v>46</v>
+      </c>
+      <c r="F97" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G97" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>1101</v>
+      </c>
+      <c r="B98" t="str">
+        <v>台泥</v>
+      </c>
+      <c r="C98">
+        <v>90000</v>
+      </c>
+      <c r="D98" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E98">
+        <v>47</v>
+      </c>
+      <c r="F98" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G98" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>2360</v>
+      </c>
+      <c r="B99" t="str">
+        <v>致茂</v>
+      </c>
+      <c r="C99">
+        <v>90000</v>
+      </c>
+      <c r="D99" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E99">
+        <v>48</v>
+      </c>
+      <c r="F99" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G99" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>5264</v>
+      </c>
+      <c r="B100" t="str">
+        <v>鎧勝-KY</v>
+      </c>
+      <c r="C100">
+        <v>85000</v>
+      </c>
+      <c r="D100" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E100">
+        <v>49</v>
+      </c>
+      <c r="F100" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G100" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>9939</v>
+      </c>
+      <c r="B101" t="str">
+        <v>宏全</v>
+      </c>
+      <c r="C101">
+        <v>80000</v>
+      </c>
+      <c r="D101" t="str">
+        <v>投信</v>
+      </c>
+      <c r="E101">
+        <v>50</v>
+      </c>
+      <c r="F101" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G101" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>2891</v>
+      </c>
+      <c r="B102" t="str">
+        <v>中信金</v>
+      </c>
+      <c r="C102">
+        <v>4422000</v>
+      </c>
+      <c r="D102" t="str">
         <v>自營商</v>
       </c>
-      <c r="E44">
+      <c r="E102">
+        <v>1</v>
+      </c>
+      <c r="F102" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G102" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>2367</v>
+      </c>
+      <c r="B103" t="str">
+        <v>燿華</v>
+      </c>
+      <c r="C103">
+        <v>3830000</v>
+      </c>
+      <c r="D103" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E103">
+        <v>2</v>
+      </c>
+      <c r="F103" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G103" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>2515</v>
+      </c>
+      <c r="B104" t="str">
+        <v>中工</v>
+      </c>
+      <c r="C104">
+        <v>2500000</v>
+      </c>
+      <c r="D104" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E104">
+        <v>3</v>
+      </c>
+      <c r="F104" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G104" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>2492</v>
+      </c>
+      <c r="B105" t="str">
+        <v>華新科</v>
+      </c>
+      <c r="C105">
+        <v>2155000</v>
+      </c>
+      <c r="D105" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E105">
+        <v>4</v>
+      </c>
+      <c r="F105" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G105" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>3706</v>
+      </c>
+      <c r="B106" t="str">
+        <v>神達</v>
+      </c>
+      <c r="C106">
+        <v>1801000</v>
+      </c>
+      <c r="D106" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E106">
+        <v>5</v>
+      </c>
+      <c r="F106" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G106" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>2327</v>
+      </c>
+      <c r="B107" t="str">
+        <v>國巨*</v>
+      </c>
+      <c r="C107">
+        <v>1350000</v>
+      </c>
+      <c r="D107" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E107">
+        <v>6</v>
+      </c>
+      <c r="F107" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G107" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>5469</v>
+      </c>
+      <c r="B108" t="str">
+        <v>瀚宇博</v>
+      </c>
+      <c r="C108">
+        <v>1158000</v>
+      </c>
+      <c r="D108" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E108">
+        <v>7</v>
+      </c>
+      <c r="F108" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G108" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>2812</v>
+      </c>
+      <c r="B109" t="str">
+        <v>台中銀</v>
+      </c>
+      <c r="C109">
+        <v>991000</v>
+      </c>
+      <c r="D109" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E109">
+        <v>8</v>
+      </c>
+      <c r="F109" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G109" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>1326</v>
+      </c>
+      <c r="B110" t="str">
+        <v>台化</v>
+      </c>
+      <c r="C110">
+        <v>875000</v>
+      </c>
+      <c r="D110" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E110">
+        <v>9</v>
+      </c>
+      <c r="F110" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G110" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>6005</v>
+      </c>
+      <c r="B111" t="str">
+        <v>群益證</v>
+      </c>
+      <c r="C111">
+        <v>839000</v>
+      </c>
+      <c r="D111" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E111">
+        <v>10</v>
+      </c>
+      <c r="F111" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G111" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>2409</v>
+      </c>
+      <c r="B112" t="str">
+        <v>友達</v>
+      </c>
+      <c r="C112">
+        <v>754000</v>
+      </c>
+      <c r="D112" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E112">
+        <v>11</v>
+      </c>
+      <c r="F112" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G112" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>1303</v>
+      </c>
+      <c r="B113" t="str">
+        <v>南亞</v>
+      </c>
+      <c r="C113">
+        <v>681000</v>
+      </c>
+      <c r="D113" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E113">
+        <v>12</v>
+      </c>
+      <c r="F113" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G113" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>1216</v>
+      </c>
+      <c r="B114" t="str">
+        <v>統一</v>
+      </c>
+      <c r="C114">
+        <v>580000</v>
+      </c>
+      <c r="D114" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E114">
+        <v>13</v>
+      </c>
+      <c r="F114" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G114" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>2448</v>
+      </c>
+      <c r="B115" t="str">
+        <v>晶電</v>
+      </c>
+      <c r="C115">
+        <v>562000</v>
+      </c>
+      <c r="D115" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E115">
+        <v>14</v>
+      </c>
+      <c r="F115" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G115" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>2352</v>
+      </c>
+      <c r="B116" t="str">
+        <v>佳世達</v>
+      </c>
+      <c r="C116">
+        <v>546000</v>
+      </c>
+      <c r="D116" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E116">
+        <v>15</v>
+      </c>
+      <c r="F116" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G116" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>2883</v>
+      </c>
+      <c r="B117" t="str">
+        <v>凱基金</v>
+      </c>
+      <c r="C117">
+        <v>537000</v>
+      </c>
+      <c r="D117" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E117">
+        <v>16</v>
+      </c>
+      <c r="F117" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G117" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>3036</v>
+      </c>
+      <c r="B118" t="str">
+        <v>文曄</v>
+      </c>
+      <c r="C118">
+        <v>532000</v>
+      </c>
+      <c r="D118" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E118">
+        <v>17</v>
+      </c>
+      <c r="F118" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G118" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>8926</v>
+      </c>
+      <c r="B119" t="str">
+        <v>台汽電</v>
+      </c>
+      <c r="C119">
+        <v>473000</v>
+      </c>
+      <c r="D119" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E119">
+        <v>18</v>
+      </c>
+      <c r="F119" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G119" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>3481</v>
+      </c>
+      <c r="B120" t="str">
+        <v>群創</v>
+      </c>
+      <c r="C120">
+        <v>424000</v>
+      </c>
+      <c r="D120" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E120">
+        <v>19</v>
+      </c>
+      <c r="F120" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G120" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>3045</v>
+      </c>
+      <c r="B121" t="str">
+        <v>台灣大</v>
+      </c>
+      <c r="C121">
+        <v>415000</v>
+      </c>
+      <c r="D121" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E121">
+        <v>20</v>
+      </c>
+      <c r="F121" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G121" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>3533</v>
+      </c>
+      <c r="B122" t="str">
+        <v>嘉澤</v>
+      </c>
+      <c r="C122">
+        <v>391000</v>
+      </c>
+      <c r="D122" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E122">
+        <v>21</v>
+      </c>
+      <c r="F122" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G122" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>1301</v>
+      </c>
+      <c r="B123" t="str">
+        <v>台塑</v>
+      </c>
+      <c r="C123">
+        <v>389000</v>
+      </c>
+      <c r="D123" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E123">
+        <v>22</v>
+      </c>
+      <c r="F123" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G123" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>1229</v>
+      </c>
+      <c r="B124" t="str">
+        <v>聯華</v>
+      </c>
+      <c r="C124">
+        <v>373000</v>
+      </c>
+      <c r="D124" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E124">
+        <v>23</v>
+      </c>
+      <c r="F124" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G124" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>3026</v>
+      </c>
+      <c r="B125" t="str">
+        <v>禾伸堂</v>
+      </c>
+      <c r="C125">
+        <v>344000</v>
+      </c>
+      <c r="D125" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E125">
+        <v>24</v>
+      </c>
+      <c r="F125" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G125" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>1536</v>
+      </c>
+      <c r="B126" t="str">
+        <v>和大</v>
+      </c>
+      <c r="C126">
+        <v>329000</v>
+      </c>
+      <c r="D126" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E126">
+        <v>25</v>
+      </c>
+      <c r="F126" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G126" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>1305</v>
+      </c>
+      <c r="B127" t="str">
+        <v>華夏</v>
+      </c>
+      <c r="C127">
+        <v>310000</v>
+      </c>
+      <c r="D127" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E127">
+        <v>26</v>
+      </c>
+      <c r="F127" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G127" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>2356</v>
+      </c>
+      <c r="B128" t="str">
+        <v>英業達</v>
+      </c>
+      <c r="C128">
+        <v>302000</v>
+      </c>
+      <c r="D128" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E128">
+        <v>27</v>
+      </c>
+      <c r="F128" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G128" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>2542</v>
+      </c>
+      <c r="B129" t="str">
+        <v>興富發</v>
+      </c>
+      <c r="C129">
+        <v>287000</v>
+      </c>
+      <c r="D129" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E129">
+        <v>28</v>
+      </c>
+      <c r="F129" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G129" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>3035</v>
+      </c>
+      <c r="B130" t="str">
+        <v>智原</v>
+      </c>
+      <c r="C130">
+        <v>257000</v>
+      </c>
+      <c r="D130" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E130">
+        <v>29</v>
+      </c>
+      <c r="F130" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G130" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>1704</v>
+      </c>
+      <c r="B131" t="str">
+        <v>榮化</v>
+      </c>
+      <c r="C131">
+        <v>255000</v>
+      </c>
+      <c r="D131" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E131">
+        <v>30</v>
+      </c>
+      <c r="F131" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G131" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>1707</v>
+      </c>
+      <c r="B132" t="str">
+        <v>葡萄王</v>
+      </c>
+      <c r="C132">
+        <v>254000</v>
+      </c>
+      <c r="D132" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E132">
+        <v>31</v>
+      </c>
+      <c r="F132" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G132" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>1455</v>
+      </c>
+      <c r="B133" t="str">
+        <v>集盛</v>
+      </c>
+      <c r="C133">
+        <v>245000</v>
+      </c>
+      <c r="D133" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E133">
+        <v>32</v>
+      </c>
+      <c r="F133" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G133" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>2324</v>
+      </c>
+      <c r="B134" t="str">
+        <v>仁寶</v>
+      </c>
+      <c r="C134">
+        <v>245000</v>
+      </c>
+      <c r="D134" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E134">
+        <v>33</v>
+      </c>
+      <c r="F134" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G134" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>5388</v>
+      </c>
+      <c r="B135" t="str">
+        <v>中磊</v>
+      </c>
+      <c r="C135">
+        <v>245000</v>
+      </c>
+      <c r="D135" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E135">
+        <v>34</v>
+      </c>
+      <c r="F135" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G135" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>1702</v>
+      </c>
+      <c r="B136" t="str">
+        <v>南僑</v>
+      </c>
+      <c r="C136">
+        <v>244000</v>
+      </c>
+      <c r="D136" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E136">
+        <v>35</v>
+      </c>
+      <c r="F136" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G136" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>3041</v>
+      </c>
+      <c r="B137" t="str">
+        <v>揚智</v>
+      </c>
+      <c r="C137">
+        <v>233000</v>
+      </c>
+      <c r="D137" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E137">
+        <v>36</v>
+      </c>
+      <c r="F137" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G137" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>2634</v>
+      </c>
+      <c r="B138" t="str">
+        <v>漢翔</v>
+      </c>
+      <c r="C138">
+        <v>232000</v>
+      </c>
+      <c r="D138" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E138">
+        <v>37</v>
+      </c>
+      <c r="F138" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G138" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>2886</v>
+      </c>
+      <c r="B139" t="str">
+        <v>兆豐金</v>
+      </c>
+      <c r="C139">
+        <v>231000</v>
+      </c>
+      <c r="D139" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E139">
+        <v>38</v>
+      </c>
+      <c r="F139" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G139" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>6283</v>
+      </c>
+      <c r="B140" t="str">
+        <v>淳安</v>
+      </c>
+      <c r="C140">
+        <v>230000</v>
+      </c>
+      <c r="D140" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E140">
+        <v>39</v>
+      </c>
+      <c r="F140" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G140" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>8105</v>
+      </c>
+      <c r="B141" t="str">
+        <v>凌巨</v>
+      </c>
+      <c r="C141">
+        <v>200000</v>
+      </c>
+      <c r="D141" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E141">
+        <v>40</v>
+      </c>
+      <c r="F141" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G141" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>2385</v>
+      </c>
+      <c r="B142" t="str">
+        <v>群光</v>
+      </c>
+      <c r="C142">
+        <v>199000</v>
+      </c>
+      <c r="D142" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E142">
+        <v>41</v>
+      </c>
+      <c r="F142" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G142" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>2357</v>
+      </c>
+      <c r="B143" t="str">
+        <v>華碩</v>
+      </c>
+      <c r="C143">
+        <v>193000</v>
+      </c>
+      <c r="D143" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E143">
+        <v>42</v>
+      </c>
+      <c r="F143" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G143" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>1802</v>
+      </c>
+      <c r="B144" t="str">
+        <v>台玻</v>
+      </c>
+      <c r="C144">
+        <v>190000</v>
+      </c>
+      <c r="D144" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E144">
+        <v>43</v>
+      </c>
+      <c r="F144" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G144" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>2823</v>
+      </c>
+      <c r="B145" t="str">
+        <v>中壽</v>
+      </c>
+      <c r="C145">
+        <v>190000</v>
+      </c>
+      <c r="D145" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E145">
+        <v>44</v>
+      </c>
+      <c r="F145" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G145" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>3231</v>
+      </c>
+      <c r="B146" t="str">
+        <v>緯創</v>
+      </c>
+      <c r="C146">
+        <v>182000</v>
+      </c>
+      <c r="D146" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E146">
+        <v>45</v>
+      </c>
+      <c r="F146" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G146" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>2313</v>
+      </c>
+      <c r="B147" t="str">
+        <v>華通</v>
+      </c>
+      <c r="C147">
+        <v>179000</v>
+      </c>
+      <c r="D147" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E147">
+        <v>46</v>
+      </c>
+      <c r="F147" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G147" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>3005</v>
+      </c>
+      <c r="B148" t="str">
+        <v>神基</v>
+      </c>
+      <c r="C148">
+        <v>175000</v>
+      </c>
+      <c r="D148" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E148">
+        <v>47</v>
+      </c>
+      <c r="F148" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G148" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>2472</v>
+      </c>
+      <c r="B149" t="str">
+        <v>立隆電</v>
+      </c>
+      <c r="C149">
+        <v>170000</v>
+      </c>
+      <c r="D149" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E149">
+        <v>48</v>
+      </c>
+      <c r="F149" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G149" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>2301</v>
+      </c>
+      <c r="B150" t="str">
+        <v>光寶科</v>
+      </c>
+      <c r="C150">
+        <v>155000</v>
+      </c>
+      <c r="D150" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E150">
+        <v>49</v>
+      </c>
+      <c r="F150" t="str">
+        <v>重複的</v>
+      </c>
+      <c r="G150" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>3014</v>
+      </c>
+      <c r="B151" t="str">
+        <v>聯陽</v>
+      </c>
+      <c r="C151">
+        <v>150000</v>
+      </c>
+      <c r="D151" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="E151">
         <v>50</v>
       </c>
-      <c r="F44" t="str">
+      <c r="F151" t="str">
+        <v>新發現個股</v>
+      </c>
+      <c r="G151" t="str">
         <v>20260612</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F44"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G151"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Stock_list.xlsx
+++ b/Stock_list.xlsx
@@ -2500,7 +2500,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G151"/>
+  <dimension ref="A1:J182"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2524,6 +2524,15 @@
       <c r="G1" t="str">
         <v>交易日期</v>
       </c>
+      <c r="H1" t="str">
+        <v>主要買超法人</v>
+      </c>
+      <c r="I1" t="str">
+        <v>當日買超張數</v>
+      </c>
+      <c r="J1" t="str">
+        <v>偵測日期</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -5975,9 +5984,536 @@
         <v>20260612</v>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>3576</v>
+      </c>
+      <c r="B152" t="str">
+        <v>聯合再生</v>
+      </c>
+      <c r="H152" t="str">
+        <v>外資</v>
+      </c>
+      <c r="I152">
+        <v>30962798</v>
+      </c>
+      <c r="J152" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>8112</v>
+      </c>
+      <c r="B153" t="str">
+        <v>至上</v>
+      </c>
+      <c r="H153" t="str">
+        <v>外資 + 投信</v>
+      </c>
+      <c r="I153">
+        <v>17926274</v>
+      </c>
+      <c r="J153" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>2406</v>
+      </c>
+      <c r="B154" t="str">
+        <v>國碩</v>
+      </c>
+      <c r="H154" t="str">
+        <v>外資</v>
+      </c>
+      <c r="I154">
+        <v>16057013</v>
+      </c>
+      <c r="J154" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>6443</v>
+      </c>
+      <c r="B155" t="str">
+        <v>元晶</v>
+      </c>
+      <c r="H155" t="str">
+        <v>外資</v>
+      </c>
+      <c r="I155">
+        <v>13937107</v>
+      </c>
+      <c r="J155" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>0056</v>
+      </c>
+      <c r="B156" t="str">
+        <v>元大高股息</v>
+      </c>
+      <c r="H156" t="str">
+        <v>外資</v>
+      </c>
+      <c r="I156">
+        <v>12930903</v>
+      </c>
+      <c r="J156" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>2867</v>
+      </c>
+      <c r="B157" t="str">
+        <v>三商壽</v>
+      </c>
+      <c r="H157" t="str">
+        <v>外資</v>
+      </c>
+      <c r="I157">
+        <v>10280930</v>
+      </c>
+      <c r="J157" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>8039</v>
+      </c>
+      <c r="B158" t="str">
+        <v>台虹</v>
+      </c>
+      <c r="H158" t="str">
+        <v>外資</v>
+      </c>
+      <c r="I158">
+        <v>7535049</v>
+      </c>
+      <c r="J158" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>2355</v>
+      </c>
+      <c r="B159" t="str">
+        <v>敬鵬</v>
+      </c>
+      <c r="H159" t="str">
+        <v>外資</v>
+      </c>
+      <c r="I159">
+        <v>6868332</v>
+      </c>
+      <c r="J159" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>1714</v>
+      </c>
+      <c r="B160" t="str">
+        <v>和桐</v>
+      </c>
+      <c r="H160" t="str">
+        <v>外資</v>
+      </c>
+      <c r="I160">
+        <v>5811300</v>
+      </c>
+      <c r="J160" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>0050</v>
+      </c>
+      <c r="B161" t="str">
+        <v>元大台灣50</v>
+      </c>
+      <c r="H161" t="str">
+        <v>外資 + 自營商</v>
+      </c>
+      <c r="I161">
+        <v>10589172</v>
+      </c>
+      <c r="J161" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>2014</v>
+      </c>
+      <c r="B162" t="str">
+        <v>中鴻</v>
+      </c>
+      <c r="H162" t="str">
+        <v>外資</v>
+      </c>
+      <c r="I162">
+        <v>5576124</v>
+      </c>
+      <c r="J162" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>2323</v>
+      </c>
+      <c r="B163" t="str">
+        <v>中環</v>
+      </c>
+      <c r="H163" t="str">
+        <v>外資</v>
+      </c>
+      <c r="I163">
+        <v>4305452</v>
+      </c>
+      <c r="J163" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>2637</v>
+      </c>
+      <c r="B164" t="str">
+        <v>慧洋-KY</v>
+      </c>
+      <c r="H164" t="str">
+        <v>外資 + 投信</v>
+      </c>
+      <c r="I164">
+        <v>6323985</v>
+      </c>
+      <c r="J164" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>2402</v>
+      </c>
+      <c r="B165" t="str">
+        <v>毅嘉</v>
+      </c>
+      <c r="H165" t="str">
+        <v>外資</v>
+      </c>
+      <c r="I165">
+        <v>3171566</v>
+      </c>
+      <c r="J165" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>6706</v>
+      </c>
+      <c r="B166" t="str">
+        <v>惠特</v>
+      </c>
+      <c r="H166" t="str">
+        <v>投信</v>
+      </c>
+      <c r="I166">
+        <v>1293000</v>
+      </c>
+      <c r="J166" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>2441</v>
+      </c>
+      <c r="B167" t="str">
+        <v>超豐</v>
+      </c>
+      <c r="H167" t="str">
+        <v>投信</v>
+      </c>
+      <c r="I167">
+        <v>875000</v>
+      </c>
+      <c r="J167" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>8021</v>
+      </c>
+      <c r="B168" t="str">
+        <v>尖點</v>
+      </c>
+      <c r="H168" t="str">
+        <v>投信 + 自營商</v>
+      </c>
+      <c r="I168">
+        <v>1250000</v>
+      </c>
+      <c r="J168" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>3532</v>
+      </c>
+      <c r="B169" t="str">
+        <v>台勝科</v>
+      </c>
+      <c r="H169" t="str">
+        <v>投信</v>
+      </c>
+      <c r="I169">
+        <v>444000</v>
+      </c>
+      <c r="J169" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>2458</v>
+      </c>
+      <c r="B170" t="str">
+        <v>義隆</v>
+      </c>
+      <c r="H170" t="str">
+        <v>投信</v>
+      </c>
+      <c r="I170">
+        <v>214853</v>
+      </c>
+      <c r="J170" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>3167</v>
+      </c>
+      <c r="B171" t="str">
+        <v>大量</v>
+      </c>
+      <c r="H171" t="str">
+        <v>投信 + 自營商</v>
+      </c>
+      <c r="I171">
+        <v>451000</v>
+      </c>
+      <c r="J171" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>5434</v>
+      </c>
+      <c r="B172" t="str">
+        <v>崇越</v>
+      </c>
+      <c r="H172" t="str">
+        <v>投信</v>
+      </c>
+      <c r="I172">
+        <v>183000</v>
+      </c>
+      <c r="J172" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>8150</v>
+      </c>
+      <c r="B173" t="str">
+        <v>南茂</v>
+      </c>
+      <c r="H173" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="I173">
+        <v>2704000</v>
+      </c>
+      <c r="J173" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>1210</v>
+      </c>
+      <c r="B174" t="str">
+        <v>大成</v>
+      </c>
+      <c r="H174" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="I174">
+        <v>1692000</v>
+      </c>
+      <c r="J174" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>2206</v>
+      </c>
+      <c r="B175" t="str">
+        <v>三陽工業</v>
+      </c>
+      <c r="H175" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="I175">
+        <v>1242696</v>
+      </c>
+      <c r="J175" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>9917</v>
+      </c>
+      <c r="B176" t="str">
+        <v>中保科</v>
+      </c>
+      <c r="H176" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="I176">
+        <v>918000</v>
+      </c>
+      <c r="J176" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>2481</v>
+      </c>
+      <c r="B177" t="str">
+        <v>強茂</v>
+      </c>
+      <c r="H177" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="I177">
+        <v>657000</v>
+      </c>
+      <c r="J177" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>8028</v>
+      </c>
+      <c r="B178" t="str">
+        <v>昇陽半導體</v>
+      </c>
+      <c r="H178" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="I178">
+        <v>238000</v>
+      </c>
+      <c r="J178" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>1215</v>
+      </c>
+      <c r="B179" t="str">
+        <v>卜蜂</v>
+      </c>
+      <c r="H179" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="I179">
+        <v>224000</v>
+      </c>
+      <c r="J179" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>2548</v>
+      </c>
+      <c r="B180" t="str">
+        <v>華固</v>
+      </c>
+      <c r="H180" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="I180">
+        <v>174000</v>
+      </c>
+      <c r="J180" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>6831</v>
+      </c>
+      <c r="B181" t="str">
+        <v>邁科</v>
+      </c>
+      <c r="H181" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="I181">
+        <v>133000</v>
+      </c>
+      <c r="J181" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>2211</v>
+      </c>
+      <c r="B182" t="str">
+        <v>長榮鋼</v>
+      </c>
+      <c r="H182" t="str">
+        <v>自營商</v>
+      </c>
+      <c r="I182">
+        <v>125434</v>
+      </c>
+      <c r="J182" t="str">
+        <v>20260612</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G151"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J182"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Stock_list.xlsx
+++ b/Stock_list.xlsx
@@ -2518,13 +2518,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>3576</v>
+        <v>0050</v>
       </c>
       <c r="B2" t="str">
-        <v>聯合再生</v>
+        <v>元大台灣50</v>
       </c>
       <c r="C2">
-        <v>30962798</v>
+        <v>5759172</v>
       </c>
       <c r="D2" t="str">
         <v>外資</v>
@@ -2532,13 +2532,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>8112</v>
+        <v>0056</v>
       </c>
       <c r="B3" t="str">
-        <v>至上</v>
+        <v>元大高股息</v>
       </c>
       <c r="C3">
-        <v>17466431</v>
+        <v>12930903</v>
       </c>
       <c r="D3" t="str">
         <v>外資</v>
@@ -2546,41 +2546,41 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2406</v>
+        <v>1210</v>
       </c>
       <c r="B4" t="str">
-        <v>國碩</v>
+        <v>大成</v>
       </c>
       <c r="C4">
-        <v>16057013</v>
+        <v>1692000</v>
       </c>
       <c r="D4" t="str">
-        <v>外資</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>6443</v>
+        <v>1215</v>
       </c>
       <c r="B5" t="str">
-        <v>元晶</v>
+        <v>卜蜂</v>
       </c>
       <c r="C5">
-        <v>13937107</v>
+        <v>224000</v>
       </c>
       <c r="D5" t="str">
-        <v>外資</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>0056</v>
+        <v>1714</v>
       </c>
       <c r="B6" t="str">
-        <v>元大高股息</v>
+        <v>和桐</v>
       </c>
       <c r="C6">
-        <v>12930903</v>
+        <v>5811300</v>
       </c>
       <c r="D6" t="str">
         <v>外資</v>
@@ -2588,13 +2588,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2867</v>
+        <v>2014</v>
       </c>
       <c r="B7" t="str">
-        <v>三商壽</v>
+        <v>中鴻</v>
       </c>
       <c r="C7">
-        <v>10280930</v>
+        <v>5576124</v>
       </c>
       <c r="D7" t="str">
         <v>外資</v>
@@ -2602,41 +2602,41 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>8039</v>
+        <v>2206</v>
       </c>
       <c r="B8" t="str">
-        <v>台虹</v>
+        <v>三陽工業</v>
       </c>
       <c r="C8">
-        <v>7535049</v>
+        <v>1242696</v>
       </c>
       <c r="D8" t="str">
-        <v>外資</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>8105</v>
+        <v>2211</v>
       </c>
       <c r="B9" t="str">
-        <v>凌巨</v>
+        <v>長榮鋼</v>
       </c>
       <c r="C9">
-        <v>7187206</v>
+        <v>125434</v>
       </c>
       <c r="D9" t="str">
-        <v>外資</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2355</v>
+        <v>2323</v>
       </c>
       <c r="B10" t="str">
-        <v>敬鵬</v>
+        <v>中環</v>
       </c>
       <c r="C10">
-        <v>6868332</v>
+        <v>4305452</v>
       </c>
       <c r="D10" t="str">
         <v>外資</v>
@@ -2644,13 +2644,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>6153</v>
+        <v>2355</v>
       </c>
       <c r="B11" t="str">
-        <v>嘉聯益</v>
+        <v>敬鵬</v>
       </c>
       <c r="C11">
-        <v>6823395</v>
+        <v>6868332</v>
       </c>
       <c r="D11" t="str">
         <v>外資</v>
@@ -2658,13 +2658,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1714</v>
+        <v>2402</v>
       </c>
       <c r="B12" t="str">
-        <v>和桐</v>
+        <v>毅嘉</v>
       </c>
       <c r="C12">
-        <v>5811300</v>
+        <v>3171566</v>
       </c>
       <c r="D12" t="str">
         <v>外資</v>
@@ -2672,13 +2672,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>0050</v>
+        <v>2406</v>
       </c>
       <c r="B13" t="str">
-        <v>元大台灣50</v>
+        <v>國碩</v>
       </c>
       <c r="C13">
-        <v>5759172</v>
+        <v>16057013</v>
       </c>
       <c r="D13" t="str">
         <v>外資</v>
@@ -2686,156 +2686,156 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2014</v>
+        <v>2441</v>
       </c>
       <c r="B14" t="str">
-        <v>中鴻</v>
+        <v>超豐</v>
       </c>
       <c r="C14">
-        <v>5576124</v>
+        <v>875000</v>
       </c>
       <c r="D14" t="str">
-        <v>外資</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2515</v>
+        <v>2455</v>
       </c>
       <c r="B15" t="str">
-        <v>中工</v>
+        <v>全新</v>
       </c>
       <c r="C15">
-        <v>4361156</v>
+        <v>147000</v>
       </c>
       <c r="D15" t="str">
-        <v>外資</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2323</v>
+        <v>2458</v>
       </c>
       <c r="B16" t="str">
-        <v>中環</v>
+        <v>義隆</v>
       </c>
       <c r="C16">
-        <v>4305452</v>
+        <v>214853</v>
       </c>
       <c r="D16" t="str">
-        <v>外資</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2637</v>
+        <v>2481</v>
       </c>
       <c r="B17" t="str">
-        <v>慧洋-KY</v>
+        <v>強茂</v>
       </c>
       <c r="C17">
-        <v>3818770</v>
+        <v>657000</v>
       </c>
       <c r="D17" t="str">
-        <v>外資</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2402</v>
+        <v>2492</v>
       </c>
       <c r="B18" t="str">
-        <v>毅嘉</v>
+        <v>華新科</v>
       </c>
       <c r="C18">
-        <v>3171566</v>
+        <v>106000</v>
       </c>
       <c r="D18" t="str">
-        <v>外資</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>6706</v>
+        <v>2515</v>
       </c>
       <c r="B19" t="str">
-        <v>惠特</v>
+        <v>中工</v>
       </c>
       <c r="C19">
-        <v>1293000</v>
+        <v>4361156</v>
       </c>
       <c r="D19" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>6278</v>
+        <v>2548</v>
       </c>
       <c r="B20" t="str">
-        <v>台表科</v>
+        <v>華固</v>
       </c>
       <c r="C20">
-        <v>981394</v>
+        <v>174000</v>
       </c>
       <c r="D20" t="str">
-        <v>投信</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2441</v>
+        <v>2637</v>
       </c>
       <c r="B21" t="str">
-        <v>超豐</v>
+        <v>慧洋-KY</v>
       </c>
       <c r="C21">
-        <v>875000</v>
+        <v>3818770</v>
       </c>
       <c r="D21" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>8021</v>
+        <v>2867</v>
       </c>
       <c r="B22" t="str">
-        <v>尖點</v>
+        <v>三商壽</v>
       </c>
       <c r="C22">
-        <v>543000</v>
+        <v>10280930</v>
       </c>
       <c r="D22" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>3532</v>
+        <v>3042</v>
       </c>
       <c r="B23" t="str">
-        <v>台勝科</v>
+        <v>晶技</v>
       </c>
       <c r="C23">
-        <v>444000</v>
+        <v>778000</v>
       </c>
       <c r="D23" t="str">
-        <v>投信</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2458</v>
+        <v>3090</v>
       </c>
       <c r="B24" t="str">
-        <v>義隆</v>
+        <v>日電貿</v>
       </c>
       <c r="C24">
-        <v>214853</v>
+        <v>3797511</v>
       </c>
       <c r="D24" t="str">
-        <v>投信</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="25">
@@ -2854,13 +2854,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>5434</v>
+        <v>3532</v>
       </c>
       <c r="B26" t="str">
-        <v>崇越</v>
+        <v>台勝科</v>
       </c>
       <c r="C26">
-        <v>183000</v>
+        <v>444000</v>
       </c>
       <c r="D26" t="str">
         <v>投信</v>
@@ -2868,27 +2868,27 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2455</v>
+        <v>3576</v>
       </c>
       <c r="B27" t="str">
-        <v>全新</v>
+        <v>聯合再生</v>
       </c>
       <c r="C27">
-        <v>147000</v>
+        <v>30962798</v>
       </c>
       <c r="D27" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>3090</v>
+        <v>4915</v>
       </c>
       <c r="B28" t="str">
-        <v>日電貿</v>
+        <v>致伸</v>
       </c>
       <c r="C28">
-        <v>3797511</v>
+        <v>1644878</v>
       </c>
       <c r="D28" t="str">
         <v>自營商</v>
@@ -2896,13 +2896,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>8150</v>
+        <v>5243</v>
       </c>
       <c r="B29" t="str">
-        <v>南茂</v>
+        <v>乙盛-KY</v>
       </c>
       <c r="C29">
-        <v>2704000</v>
+        <v>500000</v>
       </c>
       <c r="D29" t="str">
         <v>自營商</v>
@@ -2910,41 +2910,41 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>1210</v>
+        <v>5434</v>
       </c>
       <c r="B30" t="str">
-        <v>大成</v>
+        <v>崇越</v>
       </c>
       <c r="C30">
-        <v>1692000</v>
+        <v>183000</v>
       </c>
       <c r="D30" t="str">
-        <v>自營商</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>4915</v>
+        <v>6153</v>
       </c>
       <c r="B31" t="str">
-        <v>致伸</v>
+        <v>嘉聯益</v>
       </c>
       <c r="C31">
-        <v>1644878</v>
+        <v>6823395</v>
       </c>
       <c r="D31" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2206</v>
+        <v>6196</v>
       </c>
       <c r="B32" t="str">
-        <v>三陽工業</v>
+        <v>帆宣</v>
       </c>
       <c r="C32">
-        <v>1242696</v>
+        <v>623000</v>
       </c>
       <c r="D32" t="str">
         <v>自營商</v>
@@ -2966,55 +2966,55 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>9917</v>
+        <v>6278</v>
       </c>
       <c r="B34" t="str">
-        <v>中保科</v>
+        <v>台表科</v>
       </c>
       <c r="C34">
-        <v>918000</v>
+        <v>981394</v>
       </c>
       <c r="D34" t="str">
-        <v>自營商</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>3042</v>
+        <v>6443</v>
       </c>
       <c r="B35" t="str">
-        <v>晶技</v>
+        <v>元晶</v>
       </c>
       <c r="C35">
-        <v>778000</v>
+        <v>13937107</v>
       </c>
       <c r="D35" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2481</v>
+        <v>6706</v>
       </c>
       <c r="B36" t="str">
-        <v>強茂</v>
+        <v>惠特</v>
       </c>
       <c r="C36">
-        <v>657000</v>
+        <v>1293000</v>
       </c>
       <c r="D36" t="str">
-        <v>自營商</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>6196</v>
+        <v>6831</v>
       </c>
       <c r="B37" t="str">
-        <v>帆宣</v>
+        <v>邁科</v>
       </c>
       <c r="C37">
-        <v>623000</v>
+        <v>133000</v>
       </c>
       <c r="D37" t="str">
         <v>自營商</v>
@@ -3022,16 +3022,16 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>5243</v>
+        <v>8021</v>
       </c>
       <c r="B38" t="str">
-        <v>乙盛-KY</v>
+        <v>尖點</v>
       </c>
       <c r="C38">
-        <v>500000</v>
+        <v>543000</v>
       </c>
       <c r="D38" t="str">
-        <v>自營商</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="39">
@@ -3050,55 +3050,55 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>1215</v>
+        <v>8039</v>
       </c>
       <c r="B40" t="str">
-        <v>卜蜂</v>
+        <v>台虹</v>
       </c>
       <c r="C40">
-        <v>224000</v>
+        <v>7535049</v>
       </c>
       <c r="D40" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2548</v>
+        <v>8105</v>
       </c>
       <c r="B41" t="str">
-        <v>華固</v>
+        <v>凌巨</v>
       </c>
       <c r="C41">
-        <v>174000</v>
+        <v>7187206</v>
       </c>
       <c r="D41" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>6831</v>
+        <v>8112</v>
       </c>
       <c r="B42" t="str">
-        <v>邁科</v>
+        <v>至上</v>
       </c>
       <c r="C42">
-        <v>133000</v>
+        <v>17466431</v>
       </c>
       <c r="D42" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2211</v>
+        <v>8150</v>
       </c>
       <c r="B43" t="str">
-        <v>長榮鋼</v>
+        <v>南茂</v>
       </c>
       <c r="C43">
-        <v>125434</v>
+        <v>2704000</v>
       </c>
       <c r="D43" t="str">
         <v>自營商</v>
@@ -3106,13 +3106,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2492</v>
+        <v>9917</v>
       </c>
       <c r="B44" t="str">
-        <v>華新科</v>
+        <v>中保科</v>
       </c>
       <c r="C44">
-        <v>106000</v>
+        <v>918000</v>
       </c>
       <c r="D44" t="str">
         <v>自營商</v>

--- a/Stock_list.xlsx
+++ b/Stock_list.xlsx
@@ -2500,7 +2500,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D39"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2524,7 +2524,7 @@
         <v>元大台灣50</v>
       </c>
       <c r="C2">
-        <v>5759172</v>
+        <v>17368666</v>
       </c>
       <c r="D2" t="str">
         <v>外資</v>
@@ -2532,13 +2532,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>0056</v>
+        <v>0052</v>
       </c>
       <c r="B3" t="str">
-        <v>元大高股息</v>
+        <v>富邦科技</v>
       </c>
       <c r="C3">
-        <v>12930903</v>
+        <v>4678265</v>
       </c>
       <c r="D3" t="str">
         <v>外資</v>
@@ -2546,27 +2546,27 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>1210</v>
+        <v>0056</v>
       </c>
       <c r="B4" t="str">
-        <v>大成</v>
+        <v>元大高股息</v>
       </c>
       <c r="C4">
-        <v>1692000</v>
+        <v>3772314</v>
       </c>
       <c r="D4" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="B5" t="str">
-        <v>卜蜂</v>
+        <v>大成</v>
       </c>
       <c r="C5">
-        <v>224000</v>
+        <v>2357000</v>
       </c>
       <c r="D5" t="str">
         <v>自營商</v>
@@ -2580,7 +2580,7 @@
         <v>和桐</v>
       </c>
       <c r="C6">
-        <v>5811300</v>
+        <v>7453895</v>
       </c>
       <c r="D6" t="str">
         <v>外資</v>
@@ -2588,27 +2588,27 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2014</v>
+        <v>2206</v>
       </c>
       <c r="B7" t="str">
-        <v>中鴻</v>
+        <v>三陽工業</v>
       </c>
       <c r="C7">
-        <v>5576124</v>
+        <v>230000</v>
       </c>
       <c r="D7" t="str">
-        <v>外資</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2206</v>
+        <v>2211</v>
       </c>
       <c r="B8" t="str">
-        <v>三陽工業</v>
+        <v>長榮鋼</v>
       </c>
       <c r="C8">
-        <v>1242696</v>
+        <v>240000</v>
       </c>
       <c r="D8" t="str">
         <v>自營商</v>
@@ -2616,97 +2616,97 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2211</v>
+        <v>2401</v>
       </c>
       <c r="B9" t="str">
-        <v>長榮鋼</v>
+        <v>凌陽</v>
       </c>
       <c r="C9">
-        <v>125434</v>
+        <v>11996203</v>
       </c>
       <c r="D9" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2323</v>
+        <v>2441</v>
       </c>
       <c r="B10" t="str">
-        <v>中環</v>
+        <v>超豐</v>
       </c>
       <c r="C10">
-        <v>4305452</v>
+        <v>333000</v>
       </c>
       <c r="D10" t="str">
-        <v>外資</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2355</v>
+        <v>2458</v>
       </c>
       <c r="B11" t="str">
-        <v>敬鵬</v>
+        <v>義隆</v>
       </c>
       <c r="C11">
-        <v>6868332</v>
+        <v>311000</v>
       </c>
       <c r="D11" t="str">
-        <v>外資</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2402</v>
+        <v>2472</v>
       </c>
       <c r="B12" t="str">
-        <v>毅嘉</v>
+        <v>立隆電</v>
       </c>
       <c r="C12">
-        <v>3171566</v>
+        <v>252000</v>
       </c>
       <c r="D12" t="str">
-        <v>外資</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2406</v>
+        <v>2481</v>
       </c>
       <c r="B13" t="str">
-        <v>國碩</v>
+        <v>強茂</v>
       </c>
       <c r="C13">
-        <v>16057013</v>
+        <v>750500</v>
       </c>
       <c r="D13" t="str">
-        <v>外資</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2441</v>
+        <v>2489</v>
       </c>
       <c r="B14" t="str">
-        <v>超豐</v>
+        <v>瑞軒</v>
       </c>
       <c r="C14">
-        <v>875000</v>
+        <v>4957410</v>
       </c>
       <c r="D14" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2455</v>
+        <v>2637</v>
       </c>
       <c r="B15" t="str">
-        <v>全新</v>
+        <v>慧洋-KY</v>
       </c>
       <c r="C15">
-        <v>147000</v>
+        <v>339000</v>
       </c>
       <c r="D15" t="str">
         <v>投信</v>
@@ -2714,55 +2714,55 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2458</v>
+        <v>2855</v>
       </c>
       <c r="B16" t="str">
-        <v>義隆</v>
+        <v>統一證</v>
       </c>
       <c r="C16">
-        <v>214853</v>
+        <v>310000</v>
       </c>
       <c r="D16" t="str">
-        <v>投信</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2481</v>
+        <v>2867</v>
       </c>
       <c r="B17" t="str">
-        <v>強茂</v>
+        <v>三商壽</v>
       </c>
       <c r="C17">
-        <v>657000</v>
+        <v>8081270</v>
       </c>
       <c r="D17" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2492</v>
+        <v>3010</v>
       </c>
       <c r="B18" t="str">
-        <v>華新科</v>
+        <v>華立</v>
       </c>
       <c r="C18">
-        <v>106000</v>
+        <v>152000</v>
       </c>
       <c r="D18" t="str">
-        <v>自營商</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2515</v>
+        <v>3019</v>
       </c>
       <c r="B19" t="str">
-        <v>中工</v>
+        <v>亞光</v>
       </c>
       <c r="C19">
-        <v>4361156</v>
+        <v>6532731</v>
       </c>
       <c r="D19" t="str">
         <v>外資</v>
@@ -2770,13 +2770,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2548</v>
+        <v>3026</v>
       </c>
       <c r="B20" t="str">
-        <v>華固</v>
+        <v>禾伸堂</v>
       </c>
       <c r="C20">
-        <v>174000</v>
+        <v>329700</v>
       </c>
       <c r="D20" t="str">
         <v>自營商</v>
@@ -2784,13 +2784,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2637</v>
+        <v>3035</v>
       </c>
       <c r="B21" t="str">
-        <v>慧洋-KY</v>
+        <v>智原</v>
       </c>
       <c r="C21">
-        <v>3818770</v>
+        <v>5570303</v>
       </c>
       <c r="D21" t="str">
         <v>外資</v>
@@ -2798,13 +2798,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2867</v>
+        <v>3042</v>
       </c>
       <c r="B22" t="str">
-        <v>三商壽</v>
+        <v>晶技</v>
       </c>
       <c r="C22">
-        <v>10280930</v>
+        <v>9560814</v>
       </c>
       <c r="D22" t="str">
         <v>外資</v>
@@ -2812,55 +2812,55 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>3042</v>
+        <v>3048</v>
       </c>
       <c r="B23" t="str">
-        <v>晶技</v>
+        <v>益登</v>
       </c>
       <c r="C23">
-        <v>778000</v>
+        <v>5098156</v>
       </c>
       <c r="D23" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>3090</v>
+        <v>3060</v>
       </c>
       <c r="B24" t="str">
-        <v>日電貿</v>
+        <v>銘異</v>
       </c>
       <c r="C24">
-        <v>3797511</v>
+        <v>3689409</v>
       </c>
       <c r="D24" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>3167</v>
+        <v>3090</v>
       </c>
       <c r="B25" t="str">
-        <v>大量</v>
+        <v>日電貿</v>
       </c>
       <c r="C25">
-        <v>198000</v>
+        <v>1736000</v>
       </c>
       <c r="D25" t="str">
-        <v>投信</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>3532</v>
+        <v>3406</v>
       </c>
       <c r="B26" t="str">
-        <v>台勝科</v>
+        <v>玉晶光</v>
       </c>
       <c r="C26">
-        <v>444000</v>
+        <v>204000</v>
       </c>
       <c r="D26" t="str">
         <v>投信</v>
@@ -2874,7 +2874,7 @@
         <v>聯合再生</v>
       </c>
       <c r="C27">
-        <v>30962798</v>
+        <v>13477585</v>
       </c>
       <c r="D27" t="str">
         <v>外資</v>
@@ -2888,7 +2888,7 @@
         <v>致伸</v>
       </c>
       <c r="C28">
-        <v>1644878</v>
+        <v>2337000</v>
       </c>
       <c r="D28" t="str">
         <v>自營商</v>
@@ -2896,41 +2896,41 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>5243</v>
+        <v>6155</v>
       </c>
       <c r="B29" t="str">
-        <v>乙盛-KY</v>
+        <v>鈞寶</v>
       </c>
       <c r="C29">
-        <v>500000</v>
+        <v>3969493</v>
       </c>
       <c r="D29" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>5434</v>
+        <v>6191</v>
       </c>
       <c r="B30" t="str">
-        <v>崇越</v>
+        <v>精成科</v>
       </c>
       <c r="C30">
-        <v>183000</v>
+        <v>7988979</v>
       </c>
       <c r="D30" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>6153</v>
+        <v>6202</v>
       </c>
       <c r="B31" t="str">
-        <v>嘉聯益</v>
+        <v>盛群</v>
       </c>
       <c r="C31">
-        <v>6823395</v>
+        <v>5297923</v>
       </c>
       <c r="D31" t="str">
         <v>外資</v>
@@ -2938,13 +2938,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>6196</v>
+        <v>6271</v>
       </c>
       <c r="B32" t="str">
-        <v>帆宣</v>
+        <v>同欣電</v>
       </c>
       <c r="C32">
-        <v>623000</v>
+        <v>805000</v>
       </c>
       <c r="D32" t="str">
         <v>自營商</v>
@@ -2952,27 +2952,27 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>6271</v>
+        <v>6278</v>
       </c>
       <c r="B33" t="str">
-        <v>同欣電</v>
+        <v>台表科</v>
       </c>
       <c r="C33">
-        <v>1057000</v>
+        <v>203000</v>
       </c>
       <c r="D33" t="str">
-        <v>自營商</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>6278</v>
+        <v>6414</v>
       </c>
       <c r="B34" t="str">
-        <v>台表科</v>
+        <v>樺漢</v>
       </c>
       <c r="C34">
-        <v>981394</v>
+        <v>375000</v>
       </c>
       <c r="D34" t="str">
         <v>投信</v>
@@ -2980,27 +2980,27 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>6443</v>
+        <v>6768</v>
       </c>
       <c r="B35" t="str">
-        <v>元晶</v>
+        <v>志強-KY</v>
       </c>
       <c r="C35">
-        <v>13937107</v>
+        <v>265000</v>
       </c>
       <c r="D35" t="str">
-        <v>外資</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>6706</v>
+        <v>8021</v>
       </c>
       <c r="B36" t="str">
-        <v>惠特</v>
+        <v>尖點</v>
       </c>
       <c r="C36">
-        <v>1293000</v>
+        <v>527014</v>
       </c>
       <c r="D36" t="str">
         <v>投信</v>
@@ -3008,27 +3008,27 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>6831</v>
+        <v>8112</v>
       </c>
       <c r="B37" t="str">
-        <v>邁科</v>
+        <v>至上</v>
       </c>
       <c r="C37">
-        <v>133000</v>
+        <v>280000</v>
       </c>
       <c r="D37" t="str">
-        <v>自營商</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>8021</v>
+        <v>8422</v>
       </c>
       <c r="B38" t="str">
-        <v>尖點</v>
+        <v>可寧衛*</v>
       </c>
       <c r="C38">
-        <v>543000</v>
+        <v>281000</v>
       </c>
       <c r="D38" t="str">
         <v>投信</v>
@@ -3036,91 +3036,21 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>8028</v>
+        <v>9917</v>
       </c>
       <c r="B39" t="str">
-        <v>昇陽半導體</v>
+        <v>中保科</v>
       </c>
       <c r="C39">
-        <v>238000</v>
+        <v>171000</v>
       </c>
       <c r="D39" t="str">
         <v>自營商</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>8039</v>
-      </c>
-      <c r="B40" t="str">
-        <v>台虹</v>
-      </c>
-      <c r="C40">
-        <v>7535049</v>
-      </c>
-      <c r="D40" t="str">
-        <v>外資</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>8105</v>
-      </c>
-      <c r="B41" t="str">
-        <v>凌巨</v>
-      </c>
-      <c r="C41">
-        <v>7187206</v>
-      </c>
-      <c r="D41" t="str">
-        <v>外資</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>8112</v>
-      </c>
-      <c r="B42" t="str">
-        <v>至上</v>
-      </c>
-      <c r="C42">
-        <v>17466431</v>
-      </c>
-      <c r="D42" t="str">
-        <v>外資</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>8150</v>
-      </c>
-      <c r="B43" t="str">
-        <v>南茂</v>
-      </c>
-      <c r="C43">
-        <v>2704000</v>
-      </c>
-      <c r="D43" t="str">
-        <v>自營商</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>9917</v>
-      </c>
-      <c r="B44" t="str">
-        <v>中保科</v>
-      </c>
-      <c r="C44">
-        <v>918000</v>
-      </c>
-      <c r="D44" t="str">
-        <v>自營商</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D44"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D39"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Stock_list.xlsx
+++ b/Stock_list.xlsx
@@ -2500,7 +2500,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2524,7 +2524,7 @@
         <v>元大台灣50</v>
       </c>
       <c r="C2">
-        <v>17368666</v>
+        <v>6189831</v>
       </c>
       <c r="D2" t="str">
         <v>外資</v>
@@ -2538,7 +2538,7 @@
         <v>富邦科技</v>
       </c>
       <c r="C3">
-        <v>4678265</v>
+        <v>3844054</v>
       </c>
       <c r="D3" t="str">
         <v>外資</v>
@@ -2552,7 +2552,7 @@
         <v>元大高股息</v>
       </c>
       <c r="C4">
-        <v>3772314</v>
+        <v>4746150</v>
       </c>
       <c r="D4" t="str">
         <v>外資</v>
@@ -2566,7 +2566,7 @@
         <v>大成</v>
       </c>
       <c r="C5">
-        <v>2357000</v>
+        <v>913000</v>
       </c>
       <c r="D5" t="str">
         <v>自營商</v>
@@ -2574,13 +2574,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>1714</v>
+        <v>2340</v>
       </c>
       <c r="B6" t="str">
-        <v>和桐</v>
+        <v>台亞</v>
       </c>
       <c r="C6">
-        <v>7453895</v>
+        <v>3627517</v>
       </c>
       <c r="D6" t="str">
         <v>外資</v>
@@ -2588,153 +2588,153 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2206</v>
+        <v>2342</v>
       </c>
       <c r="B7" t="str">
-        <v>三陽工業</v>
+        <v>茂矽</v>
       </c>
       <c r="C7">
-        <v>230000</v>
+        <v>3390995</v>
       </c>
       <c r="D7" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2211</v>
+        <v>2399</v>
       </c>
       <c r="B8" t="str">
-        <v>長榮鋼</v>
+        <v>映泰</v>
       </c>
       <c r="C8">
-        <v>240000</v>
+        <v>4211077</v>
       </c>
       <c r="D8" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2401</v>
+        <v>2441</v>
       </c>
       <c r="B9" t="str">
-        <v>凌陽</v>
+        <v>超豐</v>
       </c>
       <c r="C9">
-        <v>11996203</v>
+        <v>1848000</v>
       </c>
       <c r="D9" t="str">
-        <v>外資</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2441</v>
+        <v>2455</v>
       </c>
       <c r="B10" t="str">
-        <v>超豐</v>
+        <v>全新</v>
       </c>
       <c r="C10">
-        <v>333000</v>
+        <v>2746065</v>
       </c>
       <c r="D10" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2458</v>
+        <v>2481</v>
       </c>
       <c r="B11" t="str">
-        <v>義隆</v>
+        <v>強茂</v>
       </c>
       <c r="C11">
-        <v>311000</v>
+        <v>885000</v>
       </c>
       <c r="D11" t="str">
-        <v>投信</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2472</v>
+        <v>2489</v>
       </c>
       <c r="B12" t="str">
-        <v>立隆電</v>
+        <v>瑞軒</v>
       </c>
       <c r="C12">
-        <v>252000</v>
+        <v>5415910</v>
       </c>
       <c r="D12" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2481</v>
+        <v>2504</v>
       </c>
       <c r="B13" t="str">
-        <v>強茂</v>
+        <v>國產</v>
       </c>
       <c r="C13">
-        <v>750500</v>
+        <v>1815121</v>
       </c>
       <c r="D13" t="str">
-        <v>投信</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2489</v>
+        <v>2855</v>
       </c>
       <c r="B14" t="str">
-        <v>瑞軒</v>
+        <v>統一證</v>
       </c>
       <c r="C14">
-        <v>4957410</v>
+        <v>594941</v>
       </c>
       <c r="D14" t="str">
-        <v>外資</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2637</v>
+        <v>2867</v>
       </c>
       <c r="B15" t="str">
-        <v>慧洋-KY</v>
+        <v>三商壽</v>
       </c>
       <c r="C15">
-        <v>339000</v>
+        <v>5768000</v>
       </c>
       <c r="D15" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2855</v>
+        <v>2889</v>
       </c>
       <c r="B16" t="str">
-        <v>統一證</v>
+        <v>國票金</v>
       </c>
       <c r="C16">
-        <v>310000</v>
+        <v>4933401</v>
       </c>
       <c r="D16" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2867</v>
+        <v>2897</v>
       </c>
       <c r="B17" t="str">
-        <v>三商壽</v>
+        <v>王道銀行</v>
       </c>
       <c r="C17">
-        <v>8081270</v>
+        <v>4443000</v>
       </c>
       <c r="D17" t="str">
         <v>外資</v>
@@ -2748,7 +2748,7 @@
         <v>華立</v>
       </c>
       <c r="C18">
-        <v>152000</v>
+        <v>843357</v>
       </c>
       <c r="D18" t="str">
         <v>投信</v>
@@ -2762,7 +2762,7 @@
         <v>亞光</v>
       </c>
       <c r="C19">
-        <v>6532731</v>
+        <v>3171876</v>
       </c>
       <c r="D19" t="str">
         <v>外資</v>
@@ -2776,7 +2776,7 @@
         <v>禾伸堂</v>
       </c>
       <c r="C20">
-        <v>329700</v>
+        <v>633000</v>
       </c>
       <c r="D20" t="str">
         <v>自營商</v>
@@ -2784,69 +2784,69 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>3035</v>
+        <v>3090</v>
       </c>
       <c r="B21" t="str">
-        <v>智原</v>
+        <v>日電貿</v>
       </c>
       <c r="C21">
-        <v>5570303</v>
+        <v>1505552</v>
       </c>
       <c r="D21" t="str">
-        <v>外資</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>3042</v>
+        <v>3167</v>
       </c>
       <c r="B22" t="str">
-        <v>晶技</v>
+        <v>大量</v>
       </c>
       <c r="C22">
-        <v>9560814</v>
+        <v>1084000</v>
       </c>
       <c r="D22" t="str">
-        <v>外資</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>3048</v>
+        <v>3563</v>
       </c>
       <c r="B23" t="str">
-        <v>益登</v>
+        <v>牧德</v>
       </c>
       <c r="C23">
-        <v>5098156</v>
+        <v>343000</v>
       </c>
       <c r="D23" t="str">
-        <v>外資</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>3060</v>
+        <v>4722</v>
       </c>
       <c r="B24" t="str">
-        <v>銘異</v>
+        <v>國精化</v>
       </c>
       <c r="C24">
-        <v>3689409</v>
+        <v>1080000</v>
       </c>
       <c r="D24" t="str">
-        <v>外資</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>3090</v>
+        <v>4915</v>
       </c>
       <c r="B25" t="str">
-        <v>日電貿</v>
+        <v>致伸</v>
       </c>
       <c r="C25">
-        <v>1736000</v>
+        <v>1422869</v>
       </c>
       <c r="D25" t="str">
         <v>自營商</v>
@@ -2854,41 +2854,41 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>3406</v>
+        <v>6209</v>
       </c>
       <c r="B26" t="str">
-        <v>玉晶光</v>
+        <v>今國光</v>
       </c>
       <c r="C26">
-        <v>204000</v>
+        <v>5011577</v>
       </c>
       <c r="D26" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>3576</v>
+        <v>6257</v>
       </c>
       <c r="B27" t="str">
-        <v>聯合再生</v>
+        <v>矽格</v>
       </c>
       <c r="C27">
-        <v>13477585</v>
+        <v>405001</v>
       </c>
       <c r="D27" t="str">
-        <v>外資</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>4915</v>
+        <v>6271</v>
       </c>
       <c r="B28" t="str">
-        <v>致伸</v>
+        <v>同欣電</v>
       </c>
       <c r="C28">
-        <v>2337000</v>
+        <v>678000</v>
       </c>
       <c r="D28" t="str">
         <v>自營商</v>
@@ -2896,41 +2896,41 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>6155</v>
+        <v>6278</v>
       </c>
       <c r="B29" t="str">
-        <v>鈞寶</v>
+        <v>台表科</v>
       </c>
       <c r="C29">
-        <v>3969493</v>
+        <v>929420</v>
       </c>
       <c r="D29" t="str">
-        <v>外資</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>6191</v>
+        <v>6414</v>
       </c>
       <c r="B30" t="str">
-        <v>精成科</v>
+        <v>樺漢</v>
       </c>
       <c r="C30">
-        <v>7988979</v>
+        <v>425000</v>
       </c>
       <c r="D30" t="str">
-        <v>外資</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>6202</v>
+        <v>8926</v>
       </c>
       <c r="B31" t="str">
-        <v>盛群</v>
+        <v>台汽電</v>
       </c>
       <c r="C31">
-        <v>5297923</v>
+        <v>3141792</v>
       </c>
       <c r="D31" t="str">
         <v>外資</v>
@@ -2938,119 +2938,21 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>6271</v>
+        <v>9907</v>
       </c>
       <c r="B32" t="str">
-        <v>同欣電</v>
+        <v>統一實</v>
       </c>
       <c r="C32">
-        <v>805000</v>
+        <v>2246689</v>
       </c>
       <c r="D32" t="str">
-        <v>自營商</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>6278</v>
-      </c>
-      <c r="B33" t="str">
-        <v>台表科</v>
-      </c>
-      <c r="C33">
-        <v>203000</v>
-      </c>
-      <c r="D33" t="str">
         <v>投信</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>6414</v>
-      </c>
-      <c r="B34" t="str">
-        <v>樺漢</v>
-      </c>
-      <c r="C34">
-        <v>375000</v>
-      </c>
-      <c r="D34" t="str">
-        <v>投信</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>6768</v>
-      </c>
-      <c r="B35" t="str">
-        <v>志強-KY</v>
-      </c>
-      <c r="C35">
-        <v>265000</v>
-      </c>
-      <c r="D35" t="str">
-        <v>投信</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>8021</v>
-      </c>
-      <c r="B36" t="str">
-        <v>尖點</v>
-      </c>
-      <c r="C36">
-        <v>527014</v>
-      </c>
-      <c r="D36" t="str">
-        <v>投信</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>8112</v>
-      </c>
-      <c r="B37" t="str">
-        <v>至上</v>
-      </c>
-      <c r="C37">
-        <v>280000</v>
-      </c>
-      <c r="D37" t="str">
-        <v>投信</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>8422</v>
-      </c>
-      <c r="B38" t="str">
-        <v>可寧衛*</v>
-      </c>
-      <c r="C38">
-        <v>281000</v>
-      </c>
-      <c r="D38" t="str">
-        <v>投信</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>9917</v>
-      </c>
-      <c r="B39" t="str">
-        <v>中保科</v>
-      </c>
-      <c r="C39">
-        <v>171000</v>
-      </c>
-      <c r="D39" t="str">
-        <v>自營商</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D32"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Stock_list.xlsx
+++ b/Stock_list.xlsx
@@ -2500,7 +2500,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2524,7 +2524,7 @@
         <v>元大台灣50</v>
       </c>
       <c r="C2">
-        <v>6189831</v>
+        <v>3116293</v>
       </c>
       <c r="D2" t="str">
         <v>外資</v>
@@ -2538,7 +2538,7 @@
         <v>富邦科技</v>
       </c>
       <c r="C3">
-        <v>3844054</v>
+        <v>4402029</v>
       </c>
       <c r="D3" t="str">
         <v>外資</v>
@@ -2552,10 +2552,10 @@
         <v>元大高股息</v>
       </c>
       <c r="C4">
-        <v>4746150</v>
+        <v>1290000</v>
       </c>
       <c r="D4" t="str">
-        <v>外資</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="5">
@@ -2566,7 +2566,7 @@
         <v>大成</v>
       </c>
       <c r="C5">
-        <v>913000</v>
+        <v>260000</v>
       </c>
       <c r="D5" t="str">
         <v>自營商</v>
@@ -2574,13 +2574,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2340</v>
+        <v>1727</v>
       </c>
       <c r="B6" t="str">
-        <v>台亞</v>
+        <v>中華化</v>
       </c>
       <c r="C6">
-        <v>3627517</v>
+        <v>3139246</v>
       </c>
       <c r="D6" t="str">
         <v>外資</v>
@@ -2588,13 +2588,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2342</v>
+        <v>2316</v>
       </c>
       <c r="B7" t="str">
-        <v>茂矽</v>
+        <v>楠梓電</v>
       </c>
       <c r="C7">
-        <v>3390995</v>
+        <v>2395033</v>
       </c>
       <c r="D7" t="str">
         <v>外資</v>
@@ -2602,13 +2602,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2399</v>
+        <v>2323</v>
       </c>
       <c r="B8" t="str">
-        <v>映泰</v>
+        <v>中環</v>
       </c>
       <c r="C8">
-        <v>4211077</v>
+        <v>4147635</v>
       </c>
       <c r="D8" t="str">
         <v>外資</v>
@@ -2616,41 +2616,41 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2441</v>
+        <v>2375</v>
       </c>
       <c r="B9" t="str">
-        <v>超豐</v>
+        <v>凱美</v>
       </c>
       <c r="C9">
-        <v>1848000</v>
+        <v>4897754</v>
       </c>
       <c r="D9" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2455</v>
+        <v>2441</v>
       </c>
       <c r="B10" t="str">
-        <v>全新</v>
+        <v>超豐</v>
       </c>
       <c r="C10">
-        <v>2746065</v>
+        <v>1702000</v>
       </c>
       <c r="D10" t="str">
-        <v>外資</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2481</v>
+        <v>2455</v>
       </c>
       <c r="B11" t="str">
-        <v>強茂</v>
+        <v>全新</v>
       </c>
       <c r="C11">
-        <v>885000</v>
+        <v>989000</v>
       </c>
       <c r="D11" t="str">
         <v>自營商</v>
@@ -2658,55 +2658,55 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2489</v>
+        <v>2472</v>
       </c>
       <c r="B12" t="str">
-        <v>瑞軒</v>
+        <v>立隆電</v>
       </c>
       <c r="C12">
-        <v>5415910</v>
+        <v>594000</v>
       </c>
       <c r="D12" t="str">
-        <v>外資</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2504</v>
+        <v>2481</v>
       </c>
       <c r="B13" t="str">
-        <v>國產</v>
+        <v>強茂</v>
       </c>
       <c r="C13">
-        <v>1815121</v>
+        <v>332000</v>
       </c>
       <c r="D13" t="str">
-        <v>自營商</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2855</v>
+        <v>2489</v>
       </c>
       <c r="B14" t="str">
-        <v>統一證</v>
+        <v>瑞軒</v>
       </c>
       <c r="C14">
-        <v>594941</v>
+        <v>5415723</v>
       </c>
       <c r="D14" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2867</v>
+        <v>2495</v>
       </c>
       <c r="B15" t="str">
-        <v>三商壽</v>
+        <v>普安</v>
       </c>
       <c r="C15">
-        <v>5768000</v>
+        <v>3134467</v>
       </c>
       <c r="D15" t="str">
         <v>外資</v>
@@ -2714,13 +2714,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2889</v>
+        <v>2501</v>
       </c>
       <c r="B16" t="str">
-        <v>國票金</v>
+        <v>國建</v>
       </c>
       <c r="C16">
-        <v>4933401</v>
+        <v>4198000</v>
       </c>
       <c r="D16" t="str">
         <v>外資</v>
@@ -2728,41 +2728,41 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2897</v>
+        <v>2504</v>
       </c>
       <c r="B17" t="str">
-        <v>王道銀行</v>
+        <v>國產</v>
       </c>
       <c r="C17">
-        <v>4443000</v>
+        <v>1377601</v>
       </c>
       <c r="D17" t="str">
-        <v>外資</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>3010</v>
+        <v>2515</v>
       </c>
       <c r="B18" t="str">
-        <v>華立</v>
+        <v>中工</v>
       </c>
       <c r="C18">
-        <v>843357</v>
+        <v>4307664</v>
       </c>
       <c r="D18" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>3019</v>
+        <v>2889</v>
       </c>
       <c r="B19" t="str">
-        <v>亞光</v>
+        <v>國票金</v>
       </c>
       <c r="C19">
-        <v>3171876</v>
+        <v>2171999</v>
       </c>
       <c r="D19" t="str">
         <v>外資</v>
@@ -2770,55 +2770,55 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>3026</v>
+        <v>2913</v>
       </c>
       <c r="B20" t="str">
-        <v>禾伸堂</v>
+        <v>農林</v>
       </c>
       <c r="C20">
-        <v>633000</v>
+        <v>2485329</v>
       </c>
       <c r="D20" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>3090</v>
+        <v>3010</v>
       </c>
       <c r="B21" t="str">
-        <v>日電貿</v>
+        <v>華立</v>
       </c>
       <c r="C21">
-        <v>1505552</v>
+        <v>621000</v>
       </c>
       <c r="D21" t="str">
-        <v>自營商</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>3167</v>
+        <v>3026</v>
       </c>
       <c r="B22" t="str">
-        <v>大量</v>
+        <v>禾伸堂</v>
       </c>
       <c r="C22">
-        <v>1084000</v>
+        <v>2153000</v>
       </c>
       <c r="D22" t="str">
-        <v>投信</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>3563</v>
+        <v>3090</v>
       </c>
       <c r="B23" t="str">
-        <v>牧德</v>
+        <v>日電貿</v>
       </c>
       <c r="C23">
-        <v>343000</v>
+        <v>302000</v>
       </c>
       <c r="D23" t="str">
         <v>投信</v>
@@ -2826,13 +2826,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>4722</v>
+        <v>3532</v>
       </c>
       <c r="B24" t="str">
-        <v>國精化</v>
+        <v>台勝科</v>
       </c>
       <c r="C24">
-        <v>1080000</v>
+        <v>807000</v>
       </c>
       <c r="D24" t="str">
         <v>自營商</v>
@@ -2840,13 +2840,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>4915</v>
+        <v>3596</v>
       </c>
       <c r="B25" t="str">
-        <v>致伸</v>
+        <v>智易</v>
       </c>
       <c r="C25">
-        <v>1422869</v>
+        <v>401000</v>
       </c>
       <c r="D25" t="str">
         <v>自營商</v>
@@ -2854,13 +2854,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>6209</v>
+        <v>3673</v>
       </c>
       <c r="B26" t="str">
-        <v>今國光</v>
+        <v>TPK-KY</v>
       </c>
       <c r="C26">
-        <v>5011577</v>
+        <v>5972587</v>
       </c>
       <c r="D26" t="str">
         <v>外資</v>
@@ -2868,41 +2868,41 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>6257</v>
+        <v>3715</v>
       </c>
       <c r="B27" t="str">
-        <v>矽格</v>
+        <v>定穎投控</v>
       </c>
       <c r="C27">
-        <v>405001</v>
+        <v>2238984</v>
       </c>
       <c r="D27" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>6271</v>
+        <v>3717</v>
       </c>
       <c r="B28" t="str">
-        <v>同欣電</v>
+        <v>聯嘉投控</v>
       </c>
       <c r="C28">
-        <v>678000</v>
+        <v>4373457</v>
       </c>
       <c r="D28" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>6278</v>
+        <v>4576</v>
       </c>
       <c r="B29" t="str">
-        <v>台表科</v>
+        <v>大銀微系統</v>
       </c>
       <c r="C29">
-        <v>929420</v>
+        <v>707000</v>
       </c>
       <c r="D29" t="str">
         <v>投信</v>
@@ -2910,49 +2910,175 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>6414</v>
+        <v>4722</v>
       </c>
       <c r="B30" t="str">
-        <v>樺漢</v>
+        <v>國精化</v>
       </c>
       <c r="C30">
-        <v>425000</v>
+        <v>859000</v>
       </c>
       <c r="D30" t="str">
-        <v>投信</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>8926</v>
+        <v>4915</v>
       </c>
       <c r="B31" t="str">
-        <v>台汽電</v>
+        <v>致伸</v>
       </c>
       <c r="C31">
-        <v>3141792</v>
+        <v>295867</v>
       </c>
       <c r="D31" t="str">
-        <v>外資</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
+        <v>6213</v>
+      </c>
+      <c r="B32" t="str">
+        <v>聯茂</v>
+      </c>
+      <c r="C32">
+        <v>3070019</v>
+      </c>
+      <c r="D32" t="str">
+        <v>外資</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>6257</v>
+      </c>
+      <c r="B33" t="str">
+        <v>矽格</v>
+      </c>
+      <c r="C33">
+        <v>248000</v>
+      </c>
+      <c r="D33" t="str">
+        <v>自營商</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>6269</v>
+      </c>
+      <c r="B34" t="str">
+        <v>台郡</v>
+      </c>
+      <c r="C34">
+        <v>5926970</v>
+      </c>
+      <c r="D34" t="str">
+        <v>外資</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>6414</v>
+      </c>
+      <c r="B35" t="str">
+        <v>樺漢</v>
+      </c>
+      <c r="C35">
+        <v>338000</v>
+      </c>
+      <c r="D35" t="str">
+        <v>投信</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>6670</v>
+      </c>
+      <c r="B36" t="str">
+        <v>復盛應用</v>
+      </c>
+      <c r="C36">
+        <v>208272</v>
+      </c>
+      <c r="D36" t="str">
+        <v>自營商</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>6962</v>
+      </c>
+      <c r="B37" t="str">
+        <v>奕力-KY</v>
+      </c>
+      <c r="C37">
+        <v>2971754</v>
+      </c>
+      <c r="D37" t="str">
+        <v>外資</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>8028</v>
+      </c>
+      <c r="B38" t="str">
+        <v>昇陽半導體</v>
+      </c>
+      <c r="C38">
+        <v>737000</v>
+      </c>
+      <c r="D38" t="str">
+        <v>投信</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>8926</v>
+      </c>
+      <c r="B39" t="str">
+        <v>台汽電</v>
+      </c>
+      <c r="C39">
+        <v>779000</v>
+      </c>
+      <c r="D39" t="str">
+        <v>自營商</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>9105</v>
+      </c>
+      <c r="B40" t="str">
+        <v>泰金寶-DR</v>
+      </c>
+      <c r="C40">
+        <v>4627000</v>
+      </c>
+      <c r="D40" t="str">
+        <v>外資</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
         <v>9907</v>
       </c>
-      <c r="B32" t="str">
+      <c r="B41" t="str">
         <v>統一實</v>
       </c>
-      <c r="C32">
-        <v>2246689</v>
-      </c>
-      <c r="D32" t="str">
+      <c r="C41">
+        <v>2252699</v>
+      </c>
+      <c r="D41" t="str">
         <v>投信</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D41"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Stock_list.xlsx
+++ b/Stock_list.xlsx
@@ -2500,7 +2500,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D37"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2524,7 +2524,7 @@
         <v>元大台灣50</v>
       </c>
       <c r="C2">
-        <v>3116293</v>
+        <v>14338704</v>
       </c>
       <c r="D2" t="str">
         <v>外資</v>
@@ -2538,7 +2538,7 @@
         <v>富邦科技</v>
       </c>
       <c r="C3">
-        <v>4402029</v>
+        <v>3671418</v>
       </c>
       <c r="D3" t="str">
         <v>外資</v>
@@ -2552,35 +2552,35 @@
         <v>元大高股息</v>
       </c>
       <c r="C4">
-        <v>1290000</v>
+        <v>8196851</v>
       </c>
       <c r="D4" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>1210</v>
+        <v>1708</v>
       </c>
       <c r="B5" t="str">
-        <v>大成</v>
+        <v>東鹼</v>
       </c>
       <c r="C5">
-        <v>260000</v>
+        <v>8110238</v>
       </c>
       <c r="D5" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>1727</v>
+        <v>1905</v>
       </c>
       <c r="B6" t="str">
-        <v>中華化</v>
+        <v>華紙</v>
       </c>
       <c r="C6">
-        <v>3139246</v>
+        <v>4721500</v>
       </c>
       <c r="D6" t="str">
         <v>外資</v>
@@ -2588,13 +2588,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2316</v>
+        <v>2323</v>
       </c>
       <c r="B7" t="str">
-        <v>楠梓電</v>
+        <v>中環</v>
       </c>
       <c r="C7">
-        <v>2395033</v>
+        <v>8395438</v>
       </c>
       <c r="D7" t="str">
         <v>外資</v>
@@ -2602,13 +2602,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2323</v>
+        <v>2340</v>
       </c>
       <c r="B8" t="str">
-        <v>中環</v>
+        <v>台亞</v>
       </c>
       <c r="C8">
-        <v>4147635</v>
+        <v>4520679</v>
       </c>
       <c r="D8" t="str">
         <v>外資</v>
@@ -2616,83 +2616,83 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2375</v>
+        <v>2351</v>
       </c>
       <c r="B9" t="str">
-        <v>凱美</v>
+        <v>順德</v>
       </c>
       <c r="C9">
-        <v>4897754</v>
+        <v>572000</v>
       </c>
       <c r="D9" t="str">
-        <v>外資</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2441</v>
+        <v>2369</v>
       </c>
       <c r="B10" t="str">
-        <v>超豐</v>
+        <v>菱生</v>
       </c>
       <c r="C10">
-        <v>1702000</v>
+        <v>4283470</v>
       </c>
       <c r="D10" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2455</v>
+        <v>2388</v>
       </c>
       <c r="B11" t="str">
-        <v>全新</v>
+        <v>威盛</v>
       </c>
       <c r="C11">
-        <v>989000</v>
+        <v>7001496</v>
       </c>
       <c r="D11" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2472</v>
+        <v>2401</v>
       </c>
       <c r="B12" t="str">
-        <v>立隆電</v>
+        <v>凌陽</v>
       </c>
       <c r="C12">
-        <v>594000</v>
+        <v>7428490</v>
       </c>
       <c r="D12" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2481</v>
+        <v>2426</v>
       </c>
       <c r="B13" t="str">
-        <v>強茂</v>
+        <v>鼎元</v>
       </c>
       <c r="C13">
-        <v>332000</v>
+        <v>12412175</v>
       </c>
       <c r="D13" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2489</v>
+        <v>2441</v>
       </c>
       <c r="B14" t="str">
-        <v>瑞軒</v>
+        <v>超豐</v>
       </c>
       <c r="C14">
-        <v>5415723</v>
+        <v>4269945</v>
       </c>
       <c r="D14" t="str">
         <v>外資</v>
@@ -2700,41 +2700,41 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2495</v>
+        <v>2455</v>
       </c>
       <c r="B15" t="str">
-        <v>普安</v>
+        <v>全新</v>
       </c>
       <c r="C15">
-        <v>3134467</v>
+        <v>2197000</v>
       </c>
       <c r="D15" t="str">
-        <v>外資</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2501</v>
+        <v>2472</v>
       </c>
       <c r="B16" t="str">
-        <v>國建</v>
+        <v>立隆電</v>
       </c>
       <c r="C16">
-        <v>4198000</v>
+        <v>1073000</v>
       </c>
       <c r="D16" t="str">
-        <v>外資</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2504</v>
+        <v>2492</v>
       </c>
       <c r="B17" t="str">
-        <v>國產</v>
+        <v>華新科</v>
       </c>
       <c r="C17">
-        <v>1377601</v>
+        <v>6603000</v>
       </c>
       <c r="D17" t="str">
         <v>自營商</v>
@@ -2742,27 +2742,27 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2515</v>
+        <v>2504</v>
       </c>
       <c r="B18" t="str">
-        <v>中工</v>
+        <v>國產</v>
       </c>
       <c r="C18">
-        <v>4307664</v>
+        <v>1670000</v>
       </c>
       <c r="D18" t="str">
-        <v>外資</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2889</v>
+        <v>2867</v>
       </c>
       <c r="B19" t="str">
-        <v>國票金</v>
+        <v>三商壽</v>
       </c>
       <c r="C19">
-        <v>2171999</v>
+        <v>4868000</v>
       </c>
       <c r="D19" t="str">
         <v>外資</v>
@@ -2770,41 +2770,41 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2913</v>
+        <v>3010</v>
       </c>
       <c r="B20" t="str">
-        <v>農林</v>
+        <v>華立</v>
       </c>
       <c r="C20">
-        <v>2485329</v>
+        <v>938000</v>
       </c>
       <c r="D20" t="str">
-        <v>外資</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>3010</v>
+        <v>3030</v>
       </c>
       <c r="B21" t="str">
-        <v>華立</v>
+        <v>德律</v>
       </c>
       <c r="C21">
-        <v>621000</v>
+        <v>292000</v>
       </c>
       <c r="D21" t="str">
-        <v>投信</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>3026</v>
+        <v>3090</v>
       </c>
       <c r="B22" t="str">
-        <v>禾伸堂</v>
+        <v>日電貿</v>
       </c>
       <c r="C22">
-        <v>2153000</v>
+        <v>2428000</v>
       </c>
       <c r="D22" t="str">
         <v>自營商</v>
@@ -2812,16 +2812,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>3090</v>
+        <v>3450</v>
       </c>
       <c r="B23" t="str">
-        <v>日電貿</v>
+        <v>聯鈞</v>
       </c>
       <c r="C23">
-        <v>302000</v>
+        <v>3573007</v>
       </c>
       <c r="D23" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="24">
@@ -2832,7 +2832,7 @@
         <v>台勝科</v>
       </c>
       <c r="C24">
-        <v>807000</v>
+        <v>307000</v>
       </c>
       <c r="D24" t="str">
         <v>自營商</v>
@@ -2846,7 +2846,7 @@
         <v>智易</v>
       </c>
       <c r="C25">
-        <v>401000</v>
+        <v>330000</v>
       </c>
       <c r="D25" t="str">
         <v>自營商</v>
@@ -2854,125 +2854,125 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>3673</v>
+        <v>4722</v>
       </c>
       <c r="B26" t="str">
-        <v>TPK-KY</v>
+        <v>國精化</v>
       </c>
       <c r="C26">
-        <v>5972587</v>
+        <v>1007000</v>
       </c>
       <c r="D26" t="str">
-        <v>外資</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>3715</v>
+        <v>4919</v>
       </c>
       <c r="B27" t="str">
-        <v>定穎投控</v>
+        <v>新唐</v>
       </c>
       <c r="C27">
-        <v>2238984</v>
+        <v>387000</v>
       </c>
       <c r="D27" t="str">
-        <v>外資</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>3717</v>
+        <v>6116</v>
       </c>
       <c r="B28" t="str">
-        <v>聯嘉投控</v>
+        <v>彩晶</v>
       </c>
       <c r="C28">
-        <v>4373457</v>
+        <v>2323000</v>
       </c>
       <c r="D28" t="str">
-        <v>外資</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>4576</v>
+        <v>6155</v>
       </c>
       <c r="B29" t="str">
-        <v>大銀微系統</v>
+        <v>鈞寶</v>
       </c>
       <c r="C29">
-        <v>707000</v>
+        <v>3121304</v>
       </c>
       <c r="D29" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>4722</v>
+        <v>6213</v>
       </c>
       <c r="B30" t="str">
-        <v>國精化</v>
+        <v>聯茂</v>
       </c>
       <c r="C30">
-        <v>859000</v>
+        <v>4330530</v>
       </c>
       <c r="D30" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>4915</v>
+        <v>6257</v>
       </c>
       <c r="B31" t="str">
-        <v>致伸</v>
+        <v>矽格</v>
       </c>
       <c r="C31">
-        <v>295867</v>
+        <v>3013121</v>
       </c>
       <c r="D31" t="str">
-        <v>自營商</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>6213</v>
+        <v>6271</v>
       </c>
       <c r="B32" t="str">
-        <v>聯茂</v>
+        <v>同欣電</v>
       </c>
       <c r="C32">
-        <v>3070019</v>
+        <v>583000</v>
       </c>
       <c r="D32" t="str">
-        <v>外資</v>
+        <v>自營商</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>6257</v>
+        <v>6278</v>
       </c>
       <c r="B33" t="str">
-        <v>矽格</v>
+        <v>台表科</v>
       </c>
       <c r="C33">
-        <v>248000</v>
+        <v>1094000</v>
       </c>
       <c r="D33" t="str">
-        <v>自營商</v>
+        <v>投信</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>6269</v>
+        <v>8105</v>
       </c>
       <c r="B34" t="str">
-        <v>台郡</v>
+        <v>凌巨</v>
       </c>
       <c r="C34">
-        <v>5926970</v>
+        <v>4156044</v>
       </c>
       <c r="D34" t="str">
         <v>外資</v>
@@ -2980,27 +2980,27 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>6414</v>
+        <v>8150</v>
       </c>
       <c r="B35" t="str">
-        <v>樺漢</v>
+        <v>南茂</v>
       </c>
       <c r="C35">
-        <v>338000</v>
+        <v>15843777</v>
       </c>
       <c r="D35" t="str">
-        <v>投信</v>
+        <v>外資</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>6670</v>
+        <v>8926</v>
       </c>
       <c r="B36" t="str">
-        <v>復盛應用</v>
+        <v>台汽電</v>
       </c>
       <c r="C36">
-        <v>208272</v>
+        <v>574000</v>
       </c>
       <c r="D36" t="str">
         <v>自營商</v>
@@ -3008,77 +3008,21 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>6962</v>
+        <v>9907</v>
       </c>
       <c r="B37" t="str">
-        <v>奕力-KY</v>
+        <v>統一實</v>
       </c>
       <c r="C37">
-        <v>2971754</v>
+        <v>2809181</v>
       </c>
       <c r="D37" t="str">
-        <v>外資</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>8028</v>
-      </c>
-      <c r="B38" t="str">
-        <v>昇陽半導體</v>
-      </c>
-      <c r="C38">
-        <v>737000</v>
-      </c>
-      <c r="D38" t="str">
-        <v>投信</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>8926</v>
-      </c>
-      <c r="B39" t="str">
-        <v>台汽電</v>
-      </c>
-      <c r="C39">
-        <v>779000</v>
-      </c>
-      <c r="D39" t="str">
-        <v>自營商</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>9105</v>
-      </c>
-      <c r="B40" t="str">
-        <v>泰金寶-DR</v>
-      </c>
-      <c r="C40">
-        <v>4627000</v>
-      </c>
-      <c r="D40" t="str">
-        <v>外資</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>9907</v>
-      </c>
-      <c r="B41" t="str">
-        <v>統一實</v>
-      </c>
-      <c r="C41">
-        <v>2252699</v>
-      </c>
-      <c r="D41" t="str">
         <v>投信</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D37"/>
   </ignoredErrors>
 </worksheet>
 </file>